--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -503,7 +503,8 @@
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -551,7 +552,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +575,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>From "Fixture Park", a fully synthetic deal built to exercise the formats. No real property is described.</t>
+          <t>From "Fixture Park", a synthetic deal built to exercise the formats. The property, its unit mix, its rent roll, its trailing-twelve statement and its pricing are fabricated. Its LOCATION is real — 505 W Baseline Rd, Tempe, AZ 85283 — so the demand, supply, rent-comp and property-tax tabs are genuine pulls from the same sources a live upload reads: the operator's own weekly rent scrape, public permit and entitlement records, Census and BLS demographics, the vendored Zillow home-value table and the vendored county rate table.</t>
         </is>
       </c>
     </row>
@@ -610,6 +611,11 @@
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Public demo</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Example (demo deal)</t>
         </is>
@@ -627,6 +633,7 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -661,6 +668,11 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
           <t>AI Underwriting Pipeline — Sample Outputs</t>
         </is>
       </c>
@@ -698,6 +710,11 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
           <t>Fixture Park</t>
         </is>
       </c>
@@ -735,6 +752,11 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
         </is>
       </c>
@@ -772,6 +794,11 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
@@ -812,6 +839,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -846,6 +878,11 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
           <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an off…</t>
         </is>
       </c>
@@ -886,6 +923,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -920,6 +962,11 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
@@ -956,6 +1003,11 @@
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -973,6 +1025,7 @@
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1007,7 +1060,12 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>1400 Example Parkway</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>505 W Baseline Rd</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1102,12 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Sample City</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Tempe</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1144,12 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1186,12 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>85283</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1228,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Example County</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1270,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Sample City MSA</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1312,12 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Street address read from the synthetic marketing package; city/state/ZIP confirmed against the same document.</t>
+          <t>Internal pipeline only — The internal pipeline geocodes the address and records how it resolved; the demo takes the address as the memorandum states it.</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -1245,6 +1333,7 @@
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1279,6 +1368,11 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
           <t>MF</t>
         </is>
       </c>
@@ -1316,6 +1410,11 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
           <t>Three-story garden, surface parked</t>
         </is>
       </c>
@@ -1353,6 +1452,11 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
@@ -1390,7 +1494,12 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>1,981</t>
         </is>
       </c>
     </row>
@@ -1427,6 +1536,11 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
           <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF), 26 three-bedroom flats (1,380 SF), 14 three-bedroom townhomes (1,620 SF). Washer/dryer …</t>
         </is>
       </c>
@@ -1464,6 +1578,11 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
           <t>Stabilized</t>
         </is>
       </c>
@@ -1501,7 +1620,12 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Delivered 2019; fully stabilized since 2021</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Delivered 1981; stabilized (synthetic operating history)</t>
         </is>
       </c>
     </row>
@@ -1517,6 +1641,7 @@
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1551,6 +1676,11 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
           <t>Sample City Residential Holdings LLC</t>
         </is>
       </c>
@@ -1588,6 +1718,11 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
           <t>Listing brokerage</t>
         </is>
       </c>
@@ -1624,6 +1759,11 @@
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>On the market</t>
         </is>
@@ -1641,6 +1781,7 @@
       <c r="E41" s="5" t="n"/>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -1675,6 +1816,11 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
           <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
@@ -1712,6 +1858,11 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
           <t>$215,000</t>
         </is>
       </c>
@@ -1724,7 +1875,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>total_price</t>
+          <t>document_price_per_unit</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1734,20 +1885,25 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Price per unit times unit count.</t>
+          <t>The per-unit price the memorandum itself states, or implies as a stated total over the unit count — the seller's figure, kept beside the price entered for comparison. None when it states no usable price.</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Offering memorandum / marketing package</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Purchase price</t>
+          <t>Pricing guidance (memorandum), for comparison</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1761,17 +1917,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>t12_cap_rate</t>
+          <t>total_price</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Trailing-twelve NOI divided by total price.</t>
+          <t>Price per unit times unit count.</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1781,10 +1937,15 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Going-in cap rate (T-12 basis)</t>
+          <t>Purchase price</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1798,7 +1959,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>t3_cap_rate</t>
+          <t>t12_cap_rate</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -1808,7 +1969,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Annualized trailing-three NOI divided by total price.</t>
+          <t>Trailing-twelve NOI divided by total price.</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1818,10 +1979,15 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Going-in cap rate (T-3 basis)</t>
+          <t>Going-in cap rate (T-12 basis)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1835,84 +2001,95 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>t3_cap_rate</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Annualized trailing-three NOI divided by total price.</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Going-in cap rate (T-3 basis)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>broker_proforma_noi</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>NOI from the broker's pro forma, when one was supplied. Kept in its own column, never merged into the T-12.</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>Offering memorandum / marketing package</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>Broker pro forma column</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>$2,332,594</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Rents</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Rents</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>in_place_rent_avg</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Weighted average in-place rent across occupied units.</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll export</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>In-place rent</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>$1,795</t>
-        </is>
-      </c>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -1922,7 +2099,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>market_rent_for_model</t>
+          <t>in_place_rent_avg</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -1932,22 +2109,27 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>The rent to underwrite: new-lease average where the plan has new leases in the lookback window, otherwise in-place. Never a blend of new and renewal.</t>
+          <t>Weighted average in-place rent across occupied units.</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Market rent / unit-mix rent</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>$1,835</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>$1,795</t>
         </is>
       </c>
     </row>
@@ -1959,84 +2141,95 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
+          <t>market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>The rent to underwrite: new-lease average where the plan has new leases in the lookback window, otherwise in-place. Never a blend of new and renewal.</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Market rent / unit-mix rent</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>$1,835</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Rents</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>fair_market_value</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Operator's own fair-market-value estimate for the asset, stated so the pricing assumption has something to be checked against. Supplied deliberately, not scraped — a field with no defined source ships blank forever.</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Supplied by the operator</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Valuation cross-check</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>$39,600,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Taxes</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Taxes</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>tax_rate_as_billed</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Millage as actually billed, not a statutory or blended rate.</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>County tax portal</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Property tax rate</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>214.8%</t>
-        </is>
-      </c>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2046,17 +2239,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>tax_rate_evidence</t>
+          <t>tax_rate_as_billed</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>What was read and from where. Reads MISSING when the portal returned nothing — a visible hole beats a plausible guess.</t>
+          <t>Millage as actually billed, not a statutory or blended rate.</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2066,12 +2259,17 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Property tax rate</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Rate as billed, 2.148 per $100 of assessed value, read from the synthetic county bill for the 2025 tax year.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>1,025.7%</t>
         </is>
       </c>
     </row>
@@ -2083,17 +2281,17 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>assessed_value_basis</t>
+          <t>tax_rate_evidence</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Value the assessment is computed against.</t>
+          <t>What was read and from where. Reads MISSING when the portal returned nothing — a visible hole beats a plausible guess.</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2103,12 +2301,17 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Tax basis</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>$23,000,000</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97: Primary rate 6.…</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2323,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>assessment_ratio</t>
+          <t>assessed_value_basis</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Share of value that is assessed.</t>
+          <t>Value the assessment is computed against.</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2140,12 +2343,17 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Tax inputs</t>
+          <t>Tax basis</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>Internal pipeline only — See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2365,17 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>tax_divisor</t>
+          <t>assessment_ratio</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Per-state divisor converting millage to a rate.</t>
+          <t>Share of value that is assessed.</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2182,7 +2390,12 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -2194,17 +2407,17 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>tax_exemption</t>
+          <t>tax_divisor</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Exemption applied against the computed bill.</t>
+          <t>Per-state divisor converting millage to a rate.</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2219,7 +2432,12 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -2231,17 +2449,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>tax_parcel_id</t>
+          <t>tax_exemption</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Assessor parcel number the bill is issued against. A tax figure that cannot name its parcel cannot be checked.</t>
+          <t>Exemption applied against the computed bill.</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2251,12 +2469,17 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Tax evidence</t>
+          <t>Tax inputs</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>SYN-000-00-000</t>
+          <t>Internal pipeline only — See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2491,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>tax_area_code</t>
+          <t>tax_parcel_id</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -2278,7 +2501,7 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Tax area / district code, which selects the published rate row that applies.</t>
+          <t>Assessor parcel number the bill is issued against. A tax figure that cannot name its parcel cannot be checked.</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2293,7 +2516,12 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>SYN-0000</t>
+          <t>Internal pipeline only — The internal pipeline reads the parcel, tax district, assessed value, exemption and billed amount off the county assessor's portal; the demo shows the county's published rate only.</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2533,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>tax_basis_label</t>
+          <t>tax_area_code</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -2315,7 +2543,7 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>What the assessed basis IS in that state — a limited value, a market value, an appraised value. The word matters because only some of them reset on sale.</t>
+          <t>Tax area / district code, which selects the published rate row that applies.</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2325,12 +2553,17 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Tax inputs</t>
+          <t>Tax evidence</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Assessed value (synthetic)</t>
+          <t>Internal pipeline only — See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2575,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>tax_basis_note</t>
+          <t>tax_basis_label</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -2352,7 +2585,7 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>How that basis behaves on a sale. Where a state caps growth and does not reset on transfer, pricing tax off the purchase price overstates it badly.</t>
+          <t>What the assessed basis IS in that state — a limited value, a market value, an appraised value. The word matters because only some of them reset on sale.</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2367,7 +2600,12 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Synthetic basis. On a real deal this row states what the basis IS in that state and whether it resets on sale.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
     </row>
@@ -2379,17 +2617,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>tax_billed_amount</t>
+          <t>tax_basis_note</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>The tax the county actually billed, for the year stated — the figure the computed tax is checked against.</t>
+          <t>How that basis behaves on a sale. Where a state caps growth and does not reset on transfer, pricing tax off the purchase price overstates it badly.</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2399,12 +2637,17 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Tax evidence</t>
+          <t>Tax inputs</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>$494,040</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. Const. art. IX sec. 18; A.R.S. sec. 42-13301) the LPV rises at most 5% a year and does not …</t>
         </is>
       </c>
     </row>
@@ -2416,17 +2659,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>tax_billed_year</t>
+          <t>tax_billed_amount</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Tax year of the billed figure.</t>
+          <t>The tax the county actually billed, for the year stated — the figure the computed tax is checked against.</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2441,7 +2684,12 @@
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Internal pipeline only — See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2453,32 +2701,37 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>computed_annual_tax</t>
+          <t>tax_billed_year</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Basis times ratio over divisor times rate, less exemption.</t>
+          <t>Tax year of the billed figure.</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>County tax portal</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Property tax expense</t>
+          <t>Tax evidence</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Internal pipeline only — See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2490,84 +2743,95 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
+          <t>computed_annual_tax</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Basis times ratio over divisor times rate, less exemption.</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Property tax expense</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
           <t>computed_tax_per_unit</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Computed annual tax divided by unit count.</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>Property tax per unit</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Closing costs</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Closing costs</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>closing_state</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>State whose statutes the closing costs are computed under. Cross-checked against the property's own state.</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Closing cost assumptions</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -2577,17 +2841,17 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>closing_price</t>
+          <t>closing_state</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Consideration the transfer tax is computed on: price per unit times unit count.</t>
+          <t>State whose statutes the closing costs are computed under. Cross-checked against the property's own state.</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2602,7 +2866,12 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>$38,700,000</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2883,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>closing_price</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -2624,22 +2893,27 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Loan the mortgage or recording tax is computed on. Absent, that tax is reported as not asserted rather than inferred from the price.</t>
+          <t>Consideration the transfer tax is computed on: price per unit times unit count.</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Debt assumptions</t>
+          <t>Closing cost assumptions</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>$38,700,000</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2925,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>transfer_tax_amount</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -2661,22 +2935,27 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>State or county real-estate transfer tax at the stated price.</t>
+          <t>Loan the mortgage or recording tax is computed on. Absent, that tax is reported as not asserted rather than inferred from the price.</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Closing costs</t>
+          <t>Debt assumptions</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2688,17 +2967,17 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>transfer_tax_rate</t>
+          <t>transfer_tax_amount</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>The rate applied, as the statute expresses it.</t>
+          <t>State or county real-estate transfer tax at the stated price.</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2713,7 +2992,12 @@
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>No real-estate transfer tax</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -2725,7 +3009,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>transfer_tax_citation</t>
+          <t>transfer_tax_rate</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -2735,7 +3019,7 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Statute or revenue-department authority for the rate — including where the authority is that no such tax exists.</t>
+          <t>The rate applied, as the statute expresses it.</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2745,12 +3029,17 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Closing costs</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Tex. Const. art. VIII, sec. 29 (added 2015)</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>No real-estate transfer tax</t>
         </is>
       </c>
     </row>
@@ -2762,17 +3051,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>mortgage_tax_amount</t>
+          <t>transfer_tax_citation</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Mortgage, intangible or recording tax on the security instrument, computed on the loan.</t>
+          <t>Statute or revenue-department authority for the rate — including where the authority is that no such tax exists.</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2782,12 +3071,17 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Closing costs</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Ariz. Const. art. IX, sec. 24 (Prop 100, 2008)</t>
         </is>
       </c>
     </row>
@@ -2799,17 +3093,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>mortgage_tax_rate</t>
+          <t>mortgage_tax_amount</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>The rate applied, as the statute expresses it.</t>
+          <t>Mortgage, intangible or recording tax on the security instrument, computed on the loan.</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2824,7 +3118,12 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>No mortgage tax</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -2836,84 +3135,95 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
+          <t>mortgage_tax_rate</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>The rate applied, as the statute expresses it.</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>Closing costs</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>No mortgage or recording tax on the security instrument</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Closing costs</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
           <t>mortgage_tax_citation</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Statute or revenue-department authority for the rate.</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>No imposing statute; Tex. Loc. Gov't Code ch. 118</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Ariz. Const. art. IX, sec. 24; A.R.S. 11-475(A)(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Schools</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>school_elementary_name</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Zoned elementary school.</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Public school-rating source</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Reference only — not a model input</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>Example Creek Elementary</t>
-        </is>
-      </c>
+      <c r="B78" s="5" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -2923,17 +3233,17 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>school_elementary_rating</t>
+          <t>school_elementary_name</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Elementary rating on a 1–10 scale.</t>
+          <t>Zoned elementary school.</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2948,7 +3258,12 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Internal pipeline only — The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2960,17 +3275,17 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>school_middle_name</t>
+          <t>school_elementary_rating</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Zoned middle school.</t>
+          <t>Elementary rating on a 1–10 scale.</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2985,7 +3300,12 @@
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>Example Ridge Middle</t>
+          <t>Internal pipeline only — The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2997,17 +3317,17 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>school_middle_rating</t>
+          <t>school_middle_name</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Middle-school rating on a 1–10 scale.</t>
+          <t>Zoned middle school.</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3022,7 +3342,12 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Internal pipeline only — The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -3034,17 +3359,17 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>school_high_name</t>
+          <t>school_middle_rating</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Zoned high school.</t>
+          <t>Middle-school rating on a 1–10 scale.</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3059,7 +3384,12 @@
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>Sample City High</t>
+          <t>Internal pipeline only — The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -3071,84 +3401,95 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
+          <t>school_high_name</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Zoned high school.</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Public school-rating source</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Schools</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
           <t>school_high_rating</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>High-school rating on a 1–10 scale.</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>Public school-rating source</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>T-12 revenue</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>T-12 revenue</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Gross Potential Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month income statement</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>Investment analysis — T-12 revenue column</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="5" t="n"/>
+      <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
+      <c r="H85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -3158,7 +3499,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Gain / (Loss) to Lease</t>
+          <t>Gross Potential Rent</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -3168,7 +3509,7 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Gain / (Loss) to Lease — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Gross Potential Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -3182,6 +3523,11 @@
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3195,7 +3541,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Gross Scheduled Rent</t>
+          <t>Gain / (Loss) to Lease</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -3205,7 +3551,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Gross Scheduled Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Gain / (Loss) to Lease — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -3219,6 +3565,11 @@
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3232,7 +3583,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Vacancy</t>
+          <t>Gross Scheduled Rent</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -3242,7 +3593,7 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Vacancy — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Gross Scheduled Rent — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -3256,6 +3607,11 @@
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3269,7 +3625,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Concessions</t>
+          <t>Vacancy</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -3279,7 +3635,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Concessions — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Vacancy — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -3293,6 +3649,11 @@
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3306,7 +3667,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Non-Revenue Units</t>
+          <t>Concessions</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -3316,7 +3677,7 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Non-Revenue Units — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Concessions — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -3330,6 +3691,11 @@
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3343,7 +3709,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Delinquency</t>
+          <t>Non-Revenue Units</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -3353,7 +3719,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Delinquency — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Non-Revenue Units — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -3367,6 +3733,11 @@
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3380,7 +3751,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Utility Reimbursements</t>
+          <t>Delinquency</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -3390,7 +3761,7 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Utility Reimbursements — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Delinquency — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -3404,6 +3775,11 @@
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3417,7 +3793,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Utility Reimbursements</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -3427,7 +3803,7 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Other Income — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Utility Reimbursements — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
@@ -3441,6 +3817,11 @@
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3454,7 +3835,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Revenue Adjustments</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -3464,7 +3845,7 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Revenue Adjustments — trailing-twelve total, and trailing-three annualized beside it.</t>
+          <t>Other Income — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -3478,6 +3859,11 @@
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3491,84 +3877,95 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
+          <t>Revenue Adjustments</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Revenue Adjustments — trailing-twelve total, and trailing-three annualized beside it.</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Trailing-twelve-month income statement</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Investment analysis — T-12 revenue column</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>T-12 revenue</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Total Revenue — trailing-twelve total, and trailing-three annualized beside it.</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Investment analysis — T-12 revenue column</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>T-12 expense</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
-      <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>T-12 expense</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>General and Administrative</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>General and Administrative — trailing-twelve total, trailing-three annualized, and per unit.</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month income statement</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Investment analysis — T-12 expense column</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -3578,7 +3975,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Leasing and Marketing</t>
+          <t>General and Administrative</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -3588,7 +3985,7 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Leasing and Marketing — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>General and Administrative — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -3602,6 +3999,11 @@
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3615,7 +4017,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Leasing and Marketing</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -3625,7 +4027,7 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Payroll — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Leasing and Marketing — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3639,6 +4041,11 @@
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3652,7 +4059,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -3662,7 +4069,7 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Insurance — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Payroll — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3676,6 +4083,11 @@
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3689,7 +4101,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Property Taxes</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -3699,7 +4111,7 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Property Taxes — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Insurance — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3713,6 +4125,11 @@
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3726,7 +4143,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Legal and Professional</t>
+          <t>Property Taxes</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -3736,7 +4153,7 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Legal and Professional — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Property Taxes — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -3750,6 +4167,11 @@
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3763,7 +4185,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Legal and Professional</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -3773,7 +4195,7 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Management Fee — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Legal and Professional — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3787,6 +4209,11 @@
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3800,7 +4227,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -3810,7 +4237,7 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Landscaping — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Management Fee — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3824,6 +4251,11 @@
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3837,7 +4269,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Repairs and Maintenance</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -3847,7 +4279,7 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Repairs and Maintenance — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Landscaping — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -3861,6 +4293,11 @@
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3874,7 +4311,7 @@
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Unit Turns</t>
+          <t>Repairs and Maintenance</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -3884,7 +4321,7 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Unit Turns — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Repairs and Maintenance — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -3898,6 +4335,11 @@
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3911,7 +4353,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Unit Turns</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -3921,7 +4363,7 @@
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Utilities — trailing-twelve total, trailing-three annualized, and per unit.</t>
+          <t>Unit Turns — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -3935,6 +4377,11 @@
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3948,84 +4395,95 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Utilities — trailing-twelve total, trailing-three annualized, and per unit.</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Trailing-twelve-month income statement</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Investment analysis — T-12 expense column</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>T-12 expense</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
           <t>Expense Adjustments</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>Expense Adjustments — trailing-twelve total, trailing-three annualized, and per unit.</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>Investment analysis — T-12 expense column</t>
         </is>
       </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>T-12 structure</t>
         </is>
       </c>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="5" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>T-12 structure</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>month_labels</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>Twelve month labels in the source statement's own order.</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month income statement</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>T-12 column headers</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -4035,30 +4493,35 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>month_order</t>
+          <t>month_labels</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Whether the months run oldest-first or newest-first. Detected from the labels, never assumed, because the T-3 window depends on it.</t>
+          <t>Twelve month labels in the source statement's own order.</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>T-12 column headers</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4072,7 +4535,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>line_item_label</t>
+          <t>month_order</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -4082,22 +4545,27 @@
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>The source statement's own wording for a line, kept verbatim beside the category it was mapped to.</t>
+          <t>Whether the months run oldest-first or newest-first. Detected from the labels, never assumed, because the T-3 window depends on it.</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>T-12 line item</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>Gross Potential Rent</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4577,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>line_item_category</t>
+          <t>line_item_label</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -4119,20 +4587,25 @@
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Which vendored category a source line was mapped to. Blank for an uncategorized subtotal, which stays visible rather than being dropped.</t>
+          <t>The source statement's own wording for a line, kept verbatim beside the category it was mapped to.</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>T-12 mapping</t>
+          <t>T-12 line item</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
         <is>
           <t>Gross Potential Rent</t>
         </is>
@@ -4146,17 +4619,17 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>line_item_t12_total</t>
+          <t>line_item_category</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Sum of a line's twelve months.</t>
+          <t>Which vendored category a source line was mapped to. Blank for an uncategorized subtotal, which stays visible rather than being dropped.</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -4166,12 +4639,17 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>T-12 column</t>
+          <t>T-12 mapping</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>Gross Potential Rent</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4661,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>line_item_t3_total</t>
+          <t>line_item_t12_total</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -4193,7 +4671,7 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Sum of a line's three most recent months, taken from whichever end the direction detector found.</t>
+          <t>Sum of a line's twelve months.</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -4203,10 +4681,15 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>T-3 column</t>
+          <t>T-12 column</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4220,7 +4703,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>gross_scheduled_rent</t>
+          <t>line_item_t3_total</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -4230,7 +4713,7 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Printed on the statement where it exists, otherwise gross potential rent plus gain/(loss) to lease. Which one fired is visible in the workbook formula.</t>
+          <t>Sum of a line's three most recent months, taken from whichever end the direction detector found.</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -4240,10 +4723,15 @@
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Gross scheduled rent</t>
+          <t>T-3 column</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4257,7 +4745,7 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>total_revenue</t>
+          <t>gross_scheduled_rent</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -4267,7 +4755,7 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Sum from gross scheduled rent down through revenue adjustments — never from gross potential rent, which double-counts loss-to-lease.</t>
+          <t>Printed on the statement where it exists, otherwise gross potential rent plus gain/(loss) to lease. Which one fired is visible in the workbook formula.</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -4277,10 +4765,15 @@
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Total revenue</t>
+          <t>Gross scheduled rent</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4294,7 +4787,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>total_operating_expenses</t>
+          <t>total_revenue</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -4304,7 +4797,7 @@
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>Sum of the twelve expense categories.</t>
+          <t>Sum from gross scheduled rent down through revenue adjustments — never from gross potential rent, which double-counts loss-to-lease.</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -4314,10 +4807,15 @@
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
+          <t>Total revenue</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4331,7 +4829,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>net_operating_income</t>
+          <t>total_operating_expenses</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -4341,7 +4839,7 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Total revenue less total operating expenses.</t>
+          <t>Sum of the twelve expense categories.</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -4351,10 +4849,15 @@
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Net operating income</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4368,7 +4871,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>t3_annualized</t>
+          <t>net_operating_income</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -4378,7 +4881,7 @@
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Trailing-three total times four, beside every rollup row.</t>
+          <t>Total revenue less total operating expenses.</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -4388,10 +4891,15 @@
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>T-3 annualized column</t>
+          <t>Net operating income</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4405,7 +4913,7 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>t6_annualized</t>
+          <t>t3_annualized</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -4415,7 +4923,7 @@
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Trailing-six total times two, so a reader can see whether the trend is up or down.</t>
+          <t>Trailing-three total times four, beside every rollup row.</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -4425,10 +4933,15 @@
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Trend cross-check</t>
+          <t>T-3 annualized column</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4442,7 +4955,7 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>expense_per_unit</t>
+          <t>t6_annualized</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -4452,7 +4965,7 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Each rollup row divided by unit count, blank-guarded so a bad unit count cannot fill the column with errors.</t>
+          <t>Trailing-six total times two, so a reader can see whether the trend is up or down.</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -4462,10 +4975,15 @@
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Per-unit expense check</t>
+          <t>Trend cross-check</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4479,17 +4997,17 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>pct_of_revenue</t>
+          <t>expense_per_unit</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Each rollup row as a share of total revenue.</t>
+          <t>Each rollup row divided by unit count, blank-guarded so a bad unit count cannot fill the column with errors.</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -4499,10 +5017,15 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Expense ratio check</t>
+          <t>Per-unit expense check</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4516,17 +5039,17 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>breakout_top4</t>
+          <t>pct_of_revenue</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>For other income, utility reimbursements, and utilities: the four largest constituent lines plus a Rest row, tying to the rollup.</t>
+          <t>Each rollup row as a share of total revenue.</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -4536,10 +5059,15 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Other-income / utility detail</t>
+          <t>Expense ratio check</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4553,30 +5081,35 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>source_subtotal</t>
+          <t>breakout_top4</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>table</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>A subtotal as printed on the source statement, kept for the cross-tie.</t>
+          <t>For other income, utility reimbursements, and utilities: the four largest constituent lines plus a Rest row, tying to the rollup.</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Other-income / utility detail</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4590,7 +5123,7 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>error_check_difference</t>
+          <t>source_subtotal</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -4600,12 +5133,12 @@
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Our category total less the source's printed subtotal. Anything over a dollar reads REVIEW rather than quietly passing.</t>
+          <t>A subtotal as printed on the source statement, kept for the cross-tie.</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Trailing-twelve-month income statement</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -4614,6 +5147,11 @@
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4627,84 +5165,95 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
+          <t>error_check_difference</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Our category total less the source's printed subtotal. Anything over a dollar reads REVIEW rather than quietly passing.</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>T-12 structure</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
           <t>absent_reason</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
         <is>
           <t>Why the T-12 section is empty, when no trailing-twelve statement was supplied. Twelve months of zeroes would validate and read as a property that earned nothing; a stated reason cannot be mistaken for one.</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F127" s="7" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>Rent roll — unit</t>
         </is>
       </c>
-      <c r="B128" s="5" t="n"/>
-      <c r="C128" s="5" t="n"/>
-      <c r="D128" s="5" t="n"/>
-      <c r="E128" s="5" t="n"/>
-      <c r="F128" s="5" t="n"/>
-      <c r="G128" s="5" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — unit</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>unit_id</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll export</t>
-        </is>
-      </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>Unit list</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>A1-101</t>
-        </is>
-      </c>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="5" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -4714,7 +5263,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>floor_plan</t>
+          <t>unit_id</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -4724,7 +5273,7 @@
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Floor-plan code the unit belongs to.</t>
+          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -4734,12 +5283,17 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Unit mix</t>
+          <t>Unit list</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>A1-101</t>
         </is>
       </c>
     </row>
@@ -4751,17 +5305,17 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>floor_plan</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms.</t>
+          <t>Floor-plan code the unit belongs to.</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -4776,7 +5330,12 @@
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>A1</t>
         </is>
       </c>
     </row>
@@ -4788,7 +5347,7 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>baths</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -4798,7 +5357,7 @@
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms.</t>
+          <t>Bedrooms.</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -4813,7 +5372,12 @@
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4825,7 +5389,7 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>sqft</t>
+          <t>baths</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -4835,7 +5399,7 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Square footage.</t>
+          <t>Bathrooms.</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -4850,7 +5414,12 @@
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -4862,17 +5431,17 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sqft</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Occupied, vacant, or model/down.</t>
+          <t>Square footage.</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -4882,12 +5451,17 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Unit mix</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>Occupied</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>720</t>
         </is>
       </c>
     </row>
@@ -4899,17 +5473,17 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>lease_start</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
+          <t>Occupied, vacant, or model/down.</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -4919,12 +5493,17 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>Occupied</t>
         </is>
       </c>
     </row>
@@ -4936,7 +5515,7 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>move_in</t>
+          <t>lease_start</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -4946,7 +5525,7 @@
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
+          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -4956,10 +5535,15 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
@@ -4973,32 +5557,37 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>lease_type</t>
+          <t>move_in</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
+          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>New-vs-renewal split</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
         </is>
       </c>
     </row>
@@ -5010,32 +5599,37 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>in_place_rent</t>
+          <t>lease_type</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>Contract rent in place.</t>
+          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>New-vs-renewal split</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>$1,535</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -5047,84 +5641,95 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
+          <t>in_place_rent</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Contract rent in place.</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>In-place rent</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>$1,535</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — unit</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
           <t>rent_per_sf</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C140" s="6" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
         <is>
           <t>In-place rent divided by square footage.</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E140" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F139" s="7" t="inlineStr">
+      <c r="F140" s="7" t="inlineStr">
         <is>
           <t>Rent per square foot</t>
         </is>
       </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>Rent roll — plan</t>
         </is>
       </c>
-      <c r="B140" s="5" t="n"/>
-      <c r="C140" s="5" t="n"/>
-      <c r="D140" s="5" t="n"/>
-      <c r="E140" s="5" t="n"/>
-      <c r="F140" s="5" t="n"/>
-      <c r="G140" s="5" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — plan</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>plan_avg_sqft</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>Average square footage for the plan.</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>Unit mix — average SF</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="n"/>
+      <c r="E141" s="5" t="n"/>
+      <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
+      <c r="H141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -5134,17 +5739,17 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>plan_units</t>
+          <t>plan_avg_sqft</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>Units in the plan.</t>
+          <t>Average square footage for the plan.</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -5154,10 +5759,15 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Unit mix — count</t>
+          <t>Unit mix — average SF</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5171,7 +5781,7 @@
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>plan_occupied</t>
+          <t>plan_units</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -5181,7 +5791,7 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Occupied units in the plan.</t>
+          <t>Units in the plan.</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -5191,10 +5801,15 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Occupancy by plan</t>
+          <t>Unit mix — count</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5208,7 +5823,7 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>plan_vacant</t>
+          <t>plan_occupied</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
@@ -5218,7 +5833,7 @@
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>Vacant units in the plan.</t>
+          <t>Occupied units in the plan.</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -5232,6 +5847,11 @@
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5245,17 +5865,17 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>plan_avg_in_place_rent</t>
+          <t>plan_vacant</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Weighted average in-place rent for the plan's occupied units.</t>
+          <t>Vacant units in the plan.</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -5265,10 +5885,15 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>In-place rent by plan</t>
+          <t>Occupancy by plan</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5282,7 +5907,7 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_rent</t>
+          <t>plan_avg_in_place_rent</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
@@ -5292,7 +5917,7 @@
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
+          <t>Weighted average in-place rent for the plan's occupied units.</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -5302,10 +5927,15 @@
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>New-lease rent evidence</t>
+          <t>In-place rent by plan</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5319,17 +5949,17 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_count</t>
+          <t>plan_new_lease_rent</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
+          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -5339,10 +5969,15 @@
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>Sample size</t>
+          <t>New-lease rent evidence</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5356,17 +5991,17 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_for_model</t>
+          <t>plan_new_lease_count</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -5376,10 +6011,15 @@
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Unit-mix market rent</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5393,84 +6033,95 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
+          <t>plan_market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>Unit-mix market rent</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
           <t>plan_market_rent_basis</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D149" s="7" t="inlineStr">
+      <c r="D150" s="7" t="inlineStr">
         <is>
           <t>Which of the two fired, stated per plan.</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E150" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F149" s="7" t="inlineStr">
+      <c r="F150" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>Rent roll — totals</t>
         </is>
       </c>
-      <c r="B150" s="5" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="n"/>
-      <c r="E150" s="5" t="n"/>
-      <c r="F150" s="5" t="n"/>
-      <c r="G150" s="5" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>total_units</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>Units on the roll.</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>Unit count cross-check</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="n"/>
+      <c r="G151" s="5" t="n"/>
+      <c r="H151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -5480,7 +6131,7 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>occupied_units</t>
+          <t>total_units</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
@@ -5490,7 +6141,7 @@
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Occupied units.</t>
+          <t>Units on the roll.</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -5500,10 +6151,15 @@
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Unit count cross-check</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5517,7 +6173,7 @@
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>vacant_units</t>
+          <t>occupied_units</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -5527,7 +6183,7 @@
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Vacant units.</t>
+          <t>Occupied units.</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
@@ -5541,6 +6197,11 @@
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5554,17 +6215,17 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>occupancy</t>
+          <t>vacant_units</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>Occupied over total.</t>
+          <t>Vacant units.</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -5574,10 +6235,15 @@
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5591,7 +6257,7 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>vacancy</t>
+          <t>occupancy</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -5601,7 +6267,7 @@
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>One less occupancy. The physical-vacancy input.</t>
+          <t>Occupied over total.</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -5615,6 +6281,11 @@
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5628,17 +6299,17 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>wavg_in_place_rent</t>
+          <t>vacancy</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted in-place rent across the property.</t>
+          <t>One less occupancy. The physical-vacancy input.</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -5648,10 +6319,15 @@
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H156" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5665,7 +6341,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>wavg_market_rent_for_model</t>
+          <t>wavg_in_place_rent</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -5675,7 +6351,7 @@
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted market rent for model across the property.</t>
+          <t>Unit-weighted in-place rent across the property.</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
@@ -5685,10 +6361,15 @@
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Market rent</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5702,17 +6383,17 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>annualized_turnover</t>
+          <t>wavg_market_rent_for_model</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Move-ins inside the lookback window, annualized against unit count.</t>
+          <t>Unit-weighted market rent for model across the property.</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -5722,10 +6403,15 @@
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Turnover assumption</t>
+          <t>Market rent</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5739,32 +6425,37 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>lookback_months</t>
+          <t>annualized_turnover</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
+          <t>Move-ins inside the lookback window, annualized against unit count.</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Turnover assumption</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5776,7 +6467,7 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>new_tenant_tolerance_days</t>
+          <t>lookback_months</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
@@ -5786,7 +6477,7 @@
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
+          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -5801,7 +6492,12 @@
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -5813,22 +6509,22 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
@@ -5838,7 +6534,12 @@
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H161" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -5850,84 +6551,95 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
           <t>roll_as_of</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D162" s="7" t="inlineStr">
+      <c r="D163" s="7" t="inlineStr">
         <is>
           <t>As-of date of the roll. Every window is measured from here.</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E163" s="6" t="inlineStr">
         <is>
           <t>Rent roll export</t>
         </is>
       </c>
-      <c r="F162" s="7" t="inlineStr">
+      <c r="F163" s="7" t="inlineStr">
         <is>
           <t>Analysis date</t>
         </is>
       </c>
-      <c r="G162" s="7" t="inlineStr">
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="5" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>Trade-out</t>
         </is>
       </c>
-      <c r="B163" s="5" t="n"/>
-      <c r="C163" s="5" t="n"/>
-      <c r="D163" s="5" t="n"/>
-      <c r="E163" s="5" t="n"/>
-      <c r="F163" s="5" t="n"/>
-      <c r="G163" s="5" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="6" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D164" s="7" t="inlineStr">
-        <is>
-          <t>New, Renewal, or First generation.</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>New-vs-renewal growth evidence</t>
-        </is>
-      </c>
-      <c r="G164" s="7" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
+      <c r="H164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -5937,17 +6649,17 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>cohort_leases</t>
+          <t>cohort</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Leases in the cohort.</t>
+          <t>New, Renewal, or First generation.</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -5957,12 +6669,17 @@
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>Sample size</t>
+          <t>New-vs-renewal growth evidence</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5974,17 +6691,17 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>cohort_prior_rent</t>
+          <t>cohort_leases</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>Average rent before the trade.</t>
+          <t>Leases in the cohort.</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -5994,12 +6711,17 @@
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Prior rent</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>$1,706</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6733,7 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_gross</t>
+          <t>cohort_prior_rent</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -6021,7 +6743,7 @@
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Average new rent before concessions.</t>
+          <t>Average rent before the trade.</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
@@ -6031,12 +6753,17 @@
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>Gross trade-out</t>
+          <t>Prior rent</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>$1,812</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6775,7 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_effective</t>
+          <t>cohort_new_rent_gross</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
@@ -6058,7 +6785,7 @@
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
+          <t>Average new rent before concessions.</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -6068,12 +6795,17 @@
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Effective trade-out</t>
+          <t>Gross trade-out</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>$1,774</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6085,30 +6817,35 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>cohort_new_rent_effective</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Effective trade-out</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6122,7 +6859,7 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>cohort_gross_change_pct</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
@@ -6132,7 +6869,7 @@
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Gross change over prior rent.</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -6146,6 +6883,11 @@
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6159,84 +6901,95 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
+          <t>cohort_effective_change_pct</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Effective change over prior rent.</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Rent growth evidence</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
           <t>absent_reason</t>
         </is>
       </c>
-      <c r="C171" s="6" t="inlineStr">
+      <c r="C172" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
+      <c r="D172" s="7" t="inlineStr">
         <is>
           <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
         </is>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E172" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="F172" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
         <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="n"/>
-      <c r="E172" s="5" t="n"/>
-      <c r="F172" s="5" t="n"/>
-      <c r="G172" s="5" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>comp_community</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D173" s="7" t="inlineStr">
-        <is>
-          <t>Comparable community name.</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>Alderwood Crossing</t>
-        </is>
-      </c>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="5" t="n"/>
+      <c r="E173" s="5" t="n"/>
+      <c r="F173" s="5" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
@@ -6246,22 +6999,22 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>comp_distance_mi</t>
+          <t>comp_community</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>Straight-line distance from the subject.</t>
+          <t>Comparable community name.</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
@@ -6271,7 +7024,12 @@
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>Ovation at Tempe</t>
         </is>
       </c>
     </row>
@@ -6283,22 +7041,22 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>comp_floor_plan</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
@@ -6308,7 +7066,12 @@
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>1BR-A</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -6320,22 +7083,22 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>comp_tier</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
@@ -6345,7 +7108,12 @@
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H176" s="7" t="inlineStr">
+        <is>
+          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
         </is>
       </c>
     </row>
@@ -6357,7 +7125,7 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -6367,12 +7135,12 @@
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
@@ -6382,7 +7150,12 @@
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>2,021</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -6394,17 +7167,17 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built_source</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -6414,12 +7187,17 @@
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>vendor note on the tracked community record</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr">
+        <is>
+          <t>1,984</t>
         </is>
       </c>
     </row>
@@ -6431,7 +7209,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>nearby_community</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -6441,7 +7219,7 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp.</t>
+          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -6451,12 +7229,17 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Rushmere Townhomes</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="inlineStr">
+        <is>
+          <t>vendor note on the tracked community record, via the market-report service</t>
         </is>
       </c>
     </row>
@@ -6468,7 +7251,7 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>nearby_address</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -6478,7 +7261,7 @@
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>Its address, so the reader can place it.</t>
+          <t>A tracked community inside the radius that is NOT a comp.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -6493,7 +7276,12 @@
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>375 Sample Street, Demo City</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
+          <t>Townhomes at Kyrene</t>
         </is>
       </c>
     </row>
@@ -6505,22 +7293,22 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>nearby_distance_mi</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -6530,7 +7318,12 @@
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
+          <t>647 W Baseline Rd, Tempe, AZ 85283-5058</t>
         </is>
       </c>
     </row>
@@ -6542,22 +7335,22 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>nearby_units</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
@@ -6567,7 +7360,12 @@
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H182" s="7" t="inlineStr">
+        <is>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -6579,22 +7377,22 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>nearby_reason</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
+          <t>Unit count where the registry has one.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
@@ -6604,7 +7402,12 @@
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>different product: tracked as bfr, subject is MF</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="inlineStr">
+        <is>
+          <t>240</t>
         </is>
       </c>
     </row>
@@ -6616,7 +7419,7 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>compset_vintage_footnote</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -6626,7 +7429,7 @@
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -6636,12 +7439,17 @@
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>Vintage filter applied where year known: +/-10 years of the subject's year built. 1 of 11 communities shown carry no published year and were matched on distance and product only.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>different product: tracked as bfr, subject is MF</t>
         </is>
       </c>
     </row>
@@ -6653,32 +7461,37 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>Vintage filter: +/-10 years of the subject's year built.</t>
         </is>
       </c>
     </row>
@@ -6690,7 +7503,7 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
@@ -6700,7 +7513,7 @@
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -6714,6 +7527,11 @@
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -6727,7 +7545,7 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
@@ -6737,7 +7555,7 @@
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
@@ -6752,7 +7570,12 @@
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6764,17 +7587,17 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -6784,12 +7607,17 @@
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>$1,450</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H188" s="7" t="inlineStr">
+        <is>
+          <t>700.0</t>
         </is>
       </c>
     </row>
@@ -6801,7 +7629,7 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -6811,7 +7639,7 @@
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -6821,12 +7649,17 @@
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>$45</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="inlineStr">
+        <is>
+          <t>$1,199</t>
         </is>
       </c>
     </row>
@@ -6838,7 +7671,7 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -6848,22 +7681,27 @@
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>$1,405</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="inlineStr">
+        <is>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -6875,7 +7713,7 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -6885,7 +7723,7 @@
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -6895,12 +7733,17 @@
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>$1,199</t>
         </is>
       </c>
     </row>
@@ -6912,32 +7755,37 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6949,17 +7797,17 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
@@ -6969,12 +7817,17 @@
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6986,17 +7839,17 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -7011,7 +7864,12 @@
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -7023,32 +7881,37 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7923,7 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -7070,7 +7933,7 @@
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -7084,6 +7947,11 @@
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7097,84 +7965,95 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
           <t>subject_vs_compset_spread</t>
         </is>
       </c>
-      <c r="C197" s="6" t="inlineStr">
+      <c r="C198" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D197" s="7" t="inlineStr">
+      <c r="D198" s="7" t="inlineStr">
         <is>
           <t>Subject market rent over comp-set net effective, less one.</t>
         </is>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E198" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F197" s="7" t="inlineStr">
+      <c r="F198" s="7" t="inlineStr">
         <is>
           <t>Rent positioning</t>
         </is>
       </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="5" t="inlineStr">
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B198" s="5" t="n"/>
-      <c r="C198" s="5" t="n"/>
-      <c r="D198" s="5" t="n"/>
-      <c r="E198" s="5" t="n"/>
-      <c r="F198" s="5" t="n"/>
-      <c r="G198" s="5" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="6" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B199" s="6" t="inlineStr">
-        <is>
-          <t>demand_ring</t>
-        </is>
-      </c>
-      <c r="C199" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D199" s="7" t="inlineStr">
-        <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F199" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G199" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="5" t="n"/>
+      <c r="E199" s="5" t="n"/>
+      <c r="F199" s="5" t="n"/>
+      <c r="G199" s="5" t="n"/>
+      <c r="H199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
@@ -7184,22 +8063,22 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>demand_population</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Population in the ring.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
@@ -7209,7 +8088,12 @@
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>9,840</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -7221,7 +8105,7 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -7231,7 +8115,7 @@
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -7246,7 +8130,12 @@
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>4,020</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>23,081</t>
         </is>
       </c>
     </row>
@@ -7258,17 +8147,17 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -7278,12 +8167,17 @@
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>$78,400</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>9,753</t>
         </is>
       </c>
     </row>
@@ -7295,17 +8189,17 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
@@ -7315,12 +8209,17 @@
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>3,150</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>$66,583</t>
         </is>
       </c>
     </row>
@@ -7332,17 +8231,17 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>demand_jobs</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Jobs located in the ring.</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -7352,12 +8251,17 @@
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="inlineStr">
+        <is>
+          <t>11,017</t>
         </is>
       </c>
     </row>
@@ -7369,84 +8273,95 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
           <t>demand_renter_share</t>
         </is>
       </c>
-      <c r="C205" s="6" t="inlineStr">
+      <c r="C206" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D205" s="7" t="inlineStr">
+      <c r="D206" s="7" t="inlineStr">
         <is>
           <t>Share of ring households that rent.</t>
         </is>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="E206" s="6" t="inlineStr">
         <is>
           <t>Public demographic data</t>
         </is>
       </c>
-      <c r="F205" s="7" t="inlineStr">
+      <c r="F206" s="7" t="inlineStr">
         <is>
           <t>Demand context</t>
         </is>
       </c>
-      <c r="G205" s="7" t="inlineStr">
-        <is>
-          <t>44.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="5" t="inlineStr">
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H206" s="7" t="inlineStr">
+        <is>
+          <t>68.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B206" s="5" t="n"/>
-      <c r="C206" s="5" t="n"/>
-      <c r="D206" s="5" t="n"/>
-      <c r="E206" s="5" t="n"/>
-      <c r="F206" s="5" t="n"/>
-      <c r="G206" s="5" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="6" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B207" s="6" t="inlineStr">
-        <is>
-          <t>supply_ring</t>
-        </is>
-      </c>
-      <c r="C207" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D207" s="7" t="inlineStr">
-        <is>
-          <t>Ring the supply row describes.</t>
-        </is>
-      </c>
-      <c r="E207" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F207" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G207" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="5" t="n"/>
+      <c r="F207" s="5" t="n"/>
+      <c r="G207" s="5" t="n"/>
+      <c r="H207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
@@ -7456,7 +8371,7 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>supply_stage</t>
+          <t>supply_ring</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
@@ -7466,12 +8381,12 @@
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
+          <t>Ring the supply row describes.</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
@@ -7481,7 +8396,12 @@
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H208" s="7" t="inlineStr">
+        <is>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -7493,17 +8413,17 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>supply_stage</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
@@ -7518,7 +8438,12 @@
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -7530,7 +8455,7 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>supply_projects</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -7540,7 +8465,7 @@
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Projects at that ring and stage.</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -7550,12 +8475,17 @@
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G210" s="7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7567,7 +8497,7 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>supply_units</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -7577,22 +8507,27 @@
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Units at that ring and stage.</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -7604,30 +8539,427 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
+          <t>supply_ring_total_units</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>All pipeline units in the ring across stages.</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H212" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
           <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D212" s="7" t="inlineStr">
+      <c r="D213" s="7" t="inlineStr">
         <is>
           <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E213" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F212" s="7" t="inlineStr">
+      <c r="F213" s="7" t="inlineStr">
         <is>
           <t>Supply pressure</t>
         </is>
       </c>
-      <c r="G212" s="7" t="inlineStr">
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H213" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="5" t="n"/>
+      <c r="F214" s="5" t="n"/>
+      <c r="G214" s="5" t="n"/>
+      <c r="H214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>om_rent_comp_community</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="inlineStr">
+        <is>
+          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>Rent comps (broker-stated)</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H215" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>om_rent_comp_distance_mi</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>Distance from the subject as the memorandum states it.</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>Rent comps (broker-stated)</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H216" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>om_rent_comp_rent</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>Rent comps (broker-stated)</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H217" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_property</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H218" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_price</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="inlineStr">
+        <is>
+          <t>The stated sale price.</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H219" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_price_per_unit</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>The stated price per unit.</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H220" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_cap_rate</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>The stated cap rate, as a fraction.</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H221" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_date</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>The sale date as written.</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7644,7 +8976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7694,7 +9026,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -7828,17 +9160,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>4 entries</t>
+          <t>434 entries</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Tracked-community registry</t>
+          <t>Tracked-community registry, via the market-report service</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>rents.communities within the radius</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -7853,7 +9185,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Every tracked community inside the radius that is not a detail row, with the reason it is not. No rent columns.</t>
+          <t>Every community the service returned that is not a detail row, with the reason.</t>
         </is>
       </c>
     </row>
@@ -7865,17 +9197,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>25 entries</t>
+          <t>27 entries</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Synthetic weekly rent scrape</t>
+          <t>Operator's own weekly rent scrape, via the market-report service</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -7903,7 +9235,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Tracked-community registry + the scrape</t>
+          <t>Tracked-community registry, via the market-report service</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -7923,7 +9255,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Tier 1 = the closest 5 matching product and vintage; tier 2 = the next 15; everything else is tier 3, identity only. An unknown year does not disqualify — it is disclosed on the tier header instead.</t>
+          <t>Closest same-product communities first, within the vintage band where the registry carries a year built; an unknown year keeps the community and says so.</t>
         </is>
       </c>
     </row>
@@ -7940,12 +9272,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -7963,22 +9295,22 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>demand.zip_home</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -7989,52 +9321,52 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
+          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A:A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="n"/>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.as_of</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -8044,36 +9376,40 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A2</t>
+          <t>Rent Roll!A:A</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
       <c r="G17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.lookback_months</t>
+          <t>rent_roll.as_of</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Synthetic rent roll export</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rent Roll!A2</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -8082,21 +9418,17 @@
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Analysis knob.</t>
-        </is>
-      </c>
+      <c r="G18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.new_tenant_tolerance_days</t>
+          <t>rent_roll.lookback_months</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -8124,22 +9456,22 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>rent_roll.new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>180 entries</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A4:K183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -8150,29 +9482,29 @@
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Unit identifiers only; the source's resident-name column is never read.</t>
+          <t>Analysis knob.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>23,000,000</t>
+          <t>180 entries</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Synthetic rent roll export</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>Rent Roll!A4:K183</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -8181,27 +9513,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
-      <c r="G21" s="13" t="n"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Unit identifiers only; the source's resident-name column is never read.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Rate table</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -8210,27 +9546,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
-      <c r="G22" s="13" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>The internal pipeline geocodes the address and records how it resolved; the demo takes the address as the memorandum states it.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Sample City</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -8239,27 +9579,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
-      <c r="G23" s="13" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Stabilized</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -8268,17 +9612,21 @@
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
-      <c r="G24" s="13" t="n"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Example County</t>
+          <t>Tempe</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -8302,12 +9650,12 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Fixture Park</t>
+          <t>Stabilized</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -8317,7 +9665,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>p.1</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -8326,21 +9674,17 @@
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Fixture Park</t>
-        </is>
-      </c>
+      <c r="G26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>On the market</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -8350,7 +9694,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>p.2</t>
+          <t>p.4</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -8364,12 +9708,12 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Delivered 2019; fully stabilized since 2021</t>
+          <t>Fixture Park</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -8379,7 +9723,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>p.1</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -8388,27 +9732,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n"/>
-      <c r="G28" s="13" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Fixture Park</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>39,600,000</t>
+          <t>On the market</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.2</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -8417,63 +9765,51 @@
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Operator's own estimate.</t>
-        </is>
-      </c>
+      <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>1,795.36</t>
+          <t>Delivered 1981; stabilized (synthetic operating history)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Unit Mix Summary!E</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Occupied units, straight off the roll.</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Listing brokerage</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -8483,29 +9819,25 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>summary.seller_entity</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n"/>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Generic label; no firm or individual is named in a published file.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>1,834.78</t>
+          <t>1,795.36</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -8515,7 +9847,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Unit Mix Summary!H</t>
+          <t>Unit Mix Summary!E</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -8530,19 +9862,19 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
+          <t>Occupied units, straight off the roll.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Sample City MSA</t>
+          <t>Listing brokerage</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -8562,96 +9894,108 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>summary.city, summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Metro assigned from the city/state pair.</t>
+          <t>Generic label; no firm or individual is named in a published file.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>1,834.78</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Unit Mix Summary!H</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="n"/>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Illustrative figure supplied directly; not a quote or an offer.</t>
+          <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF…</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="13" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>summary.city, summary.state</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Metro assigned from the city/state pair.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>summary.product_type</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -8660,27 +10004,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n"/>
-      <c r="G36" s="13" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Illustrative figure supplied directly; not a quote or an offer.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_detail</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Example Creek Elementary</t>
+          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF…</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>School attendance lookup</t>
+          <t>p.7</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -8694,22 +10042,22 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Sample City High</t>
+          <t>MF</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>School attendance lookup</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -8723,22 +10071,22 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Example Ridge Middle</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>School attendance lookup</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -8747,27 +10095,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n"/>
-      <c r="G39" s="13" t="n"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Sample City Residential Holdings LLC</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>p.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -8776,27 +10128,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n"/>
-      <c r="G40" s="13" t="n"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -8805,17 +10161,21 @@
         </is>
       </c>
       <c r="F41" s="12" t="n"/>
-      <c r="G41" s="13" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>1400 Example Parkway</t>
+          <t>Sample City Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -8825,7 +10185,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>p.2</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -8834,21 +10194,17 @@
         </is>
       </c>
       <c r="F42" s="12" t="n"/>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>1400 Example Parkway</t>
-        </is>
-      </c>
+      <c r="G42" s="13" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Three-story garden, surface parked</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -8858,7 +10214,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>p.4</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -8867,31 +10223,27 @@
         </is>
       </c>
       <c r="F43" s="12" t="n"/>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>Three-story garden, surface parked</t>
-        </is>
-      </c>
+      <c r="G43" s="13" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>SYN-0000</t>
+          <t>505 W Baseline Rd</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Rate table</t>
+          <t>p.4</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -8900,27 +10252,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n"/>
-      <c r="G44" s="13" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>1400 Example Parkway</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Assessed value (synthetic)</t>
+          <t>Three-story garden, surface parked</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Synthetic offering memorandum</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>p.6</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -8929,27 +10285,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n"/>
-      <c r="G45" s="13" t="n"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Three-story garden, surface parked</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Synthetic basis. On a real deal this row states what the basis IS in that state and whe…</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -8958,27 +10318,31 @@
         </is>
       </c>
       <c r="F46" s="12" t="n"/>
-      <c r="G46" s="13" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>494,040</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Tax bill</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -8987,27 +10351,31 @@
         </is>
       </c>
       <c r="F47" s="12" t="n"/>
-      <c r="G47" s="13" t="n"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>What the assessed basis is in this state.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Tax bill</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -9016,27 +10384,31 @@
         </is>
       </c>
       <c r="F48" s="12" t="n"/>
-      <c r="G48" s="13" t="n"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>How the basis behaves on a sale, with the authority.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Rate table</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -9045,27 +10417,31 @@
         </is>
       </c>
       <c r="F49" s="12" t="n"/>
-      <c r="G49" s="13" t="n"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Valuation notice</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -9074,27 +10450,31 @@
         </is>
       </c>
       <c r="F50" s="12" t="n"/>
-      <c r="G50" s="13" t="n"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>SYN-000-00-000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Parcel record</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -9103,27 +10483,31 @@
         </is>
       </c>
       <c r="F51" s="12" t="n"/>
-      <c r="G51" s="13" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Synthetic county tax record</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Rate table, synthetic district</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -9132,93 +10516,101 @@
         </is>
       </c>
       <c r="F52" s="12" t="n"/>
-      <c r="G52" s="13" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A:A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n"/>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>Distinct unit identifiers on the roll.</t>
+          <t>The internal pipeline reads the parcel, tax district, assessed value, exemption and billed amount off the county assessor's portal; the demo shows the county's published rate only.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2,019</t>
+          <t>OUTSIDE the band (the statement's line per unit): $2,797 per unit a year is outside the…</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="n"/>
-      <c r="G54" s="13" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -9227,60 +10619,68 @@
         </is>
       </c>
       <c r="F55" s="12" t="n"/>
-      <c r="G55" s="13" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>supply.rings</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Synthetic public data extract</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Permit and entitlement records.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Synthetic trailing-twelve income statement</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>T-12!C8:N8</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -9291,47 +10691,51 @@
       <c r="F57" s="12" t="n"/>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>5 keys</t>
+          <t>503,391.9</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Synthetic trailing-twelve income statement</t>
+          <t>the synthetic trailing-twelve statement</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>T-12!O</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="n"/>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>t12.rows</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>The statement's own printed subtotals, kept for the cross-tie.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -9346,7 +10750,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rent Roll!A:A</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -9356,41 +10760,235 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
-      <c r="G59" s="13" t="n"/>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Distinct unit identifiers on the roll.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
+          <t>summary.year_built</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>1,981</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>p.6</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="13" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>summary.zip</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>85283</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic offering memorandum</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>p.4</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="13" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>supply.rings</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>8 entries</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>t12.month_labels</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>12 entries</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic trailing-twelve income statement</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>T-12!C8:N8</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n"/>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>t12.source_subtotals</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>5 keys</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic trailing-twelve income statement</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>T-12!O</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>The statement's own printed subtotals, kept for the cross-tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>t12.units</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Synthetic rent roll export</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
           <t>trade_out.rows</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>3 entries</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Synthetic lease trade-out report</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>0 entries</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Internal pipeline only</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Cohort averages.</t>
+      <c r="F66" s="12" t="n"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -9160,7 +9160,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>434 entries</t>
+          <t>446 entries</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>From "Fixture Park", a synthetic deal built to exercise the formats. The property, its unit mix, its rent roll, its trailing-twelve statement and its pricing are fabricated. Its LOCATION is real — 505 W Baseline Rd, Tempe, AZ 85283 — so the demand, supply, rent-comp and property-tax tabs are genuine pulls from the same sources a live upload reads: the operator's own weekly rent scrape, public permit and entitlement records, Census and BLS demographics, the vendored Zillow home-value table and the vendored county rate table.</t>
+          <t>From "Southern Avenue Sample". Pricing is illustrative; see the deal summary for the boundary note.</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Fixture Park</t>
+          <t>Southern Avenue Sample</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen to sit inside the band a real per-unit sale price occupies; it is not a quote, an off…</t>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote…</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>505 W Baseline Rd</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>Mesa</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>85204</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>garden-style multifamily</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Three-story garden, surface parked</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>334</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF), 26 three-bedroom flats (1,380 SF), 14 three-bedroom townhomes (1,620 SF). Washer/dryer …</t>
+          <t>One-, two-, and three-bedroom residences averaging 856 square feet across 40 buildings on 15.87 acres</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Stabilized</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Delivered 1981; stabilized (synthetic operating history)</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Sample City Residential Holdings LLC</t>
+          <t>Institutional owner-operator (name withheld)</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>On the market</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>$2,332,594</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>$1,795</t>
+          <t>$1,457</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>$1,835</t>
+          <t>$1,345</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>301-04-002K</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>$249,122</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>2,025</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>$38,700,000</t>
+          <t>$71,810,000</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Gross Potential Rent</t>
+          <t>MARKET RENT (1016)</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>A1-101</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>3X2B</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>1,444.0</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2019-09-25</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>$1,535</t>
+          <t>$2,258</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
+          <t>The upload demo does not ask for a lease trade-out report, so there is no basis for a new-versus-renewal block.</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
-          <t>Ovation at Tempe</t>
+          <t>Saltera Apartments</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Townhomes at Kyrene</t>
+          <t>Trails at Harris</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>647 W Baseline Rd, Tempe, AZ 85283-5058</t>
+          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>different product: tracked as bfr, subject is MF</t>
+          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>688.0</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>$1,199</t>
+          <t>$1,047</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>$1,199</t>
+          <t>$1,047</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>23,081</t>
+          <t>20,297</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>9,753</t>
+          <t>7,711</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>$66,583</t>
+          <t>$79,735</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>11,017</t>
+          <t>5,239</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>-2.0%</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8998,7 +8998,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Fixture Park — as of 2026-06-30</t>
+          <t>Southern Avenue Sample — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -9091,27 +9091,23 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Vendored state rate table</t>
+          <t>Not run in the upload demo</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>closing_costs.MORTGAGE_TAX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>closing_costs.loan_amount, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n"/>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Computed on the LOAN, never on the price. With no loan amount the line is reported as not asserted rather than inferred at 100% leverage.</t>
+          <t>Not run in the upload demo. This section needs data sources the demo does not reach, so it is left empty rather than filled with placeholders.</t>
         </is>
       </c>
     </row>
@@ -9128,27 +9124,23 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Vendored state rate table</t>
+          <t>Not run in the upload demo</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>closing_costs.TRANSFER_TAX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>pricing.price_per_unit, pricing.unit_count, summary.state, closing_costs.price</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Rate applied to price_per_unit x unit_count. Per-unit statutes round the consideration up.</t>
+          <t>Not run in the upload demo. This section needs data sources the demo does not reach, so it is left empty rather than filled with placeholders.</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9152,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>446 entries</t>
+          <t>340 entries</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -9197,7 +9189,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>27 entries</t>
+          <t>19 entries</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -9328,22 +9320,22 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>om_comps.rent</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -9354,91 +9346,99 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Illustrative. Inside the band a per-unit sale price occupies.</t>
+          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A:A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="n"/>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.as_of</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="13" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.lookback_months</t>
+          <t>rent_roll.as_of</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>as-of line</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -9449,24 +9449,24 @@
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Analysis knob.</t>
+          <t>Read as the end of the period the roll's own header states.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.new_tenant_tolerance_days</t>
+          <t>rent_roll.lookback_months</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -9482,29 +9482,29 @@
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Analysis knob.</t>
+          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>rent_roll.new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>180 entries</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A4:K183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -9515,29 +9515,29 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Unit identifiers only; the source's resident-name column is never read.</t>
+          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>summary.address_provenance</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>334 entries</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -9548,24 +9548,24 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline geocodes the address and records how it resolved; the demo takes the address as the memorandum states it.</t>
+          <t>Read from the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -9581,29 +9581,29 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -9614,29 +9614,29 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Tempe</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -9645,27 +9645,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
-      <c r="G25" s="13" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Stabilized</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -9674,27 +9678,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
-      <c r="G26" s="13" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -9703,27 +9711,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
-      <c r="G27" s="13" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Fixture Park</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>p.1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -9734,29 +9746,29 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Fixture Park</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>On the market</t>
+          <t>Southern Avenue Sample</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Illustrative</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>p.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -9765,27 +9777,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
-      <c r="G29" s="13" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>The sample's name is illustrative; the asset's real name is withheld.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Delivered 1981; stabilized (synthetic operating history)</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -9794,12 +9810,16 @@
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
-      <c r="G30" s="13" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -9809,7 +9829,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -9825,61 +9845,57 @@
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>1,795.36</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Unit Mix Summary!E</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>Occupied units, straight off the roll.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Listing brokerage</t>
+          <t>1,456.99</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -9894,66 +9910,62 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Generic label; no firm or individual is named in a published file.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>1,834.78</t>
+          <t>Listing brokerage</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Unit Mix Summary!H</t>
+          <t>withheld</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n"/>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>New-lease average where a plan has new leases in the window, else in-place. Never a blend.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>1,344.6</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -9968,29 +9980,29 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>summary.city, summary.state</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Metro assigned from the city/state pair.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -10006,29 +10018,29 @@
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Illustrative figure supplied directly; not a quote or an offer.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>180 units across six plans: 62 one-bedroom (720–795 SF), 78 two-bedroom (1,050–1,140 SF…</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>p.7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -10037,27 +10049,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n"/>
-      <c r="G37" s="13" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>summary.product_type</t>
+          <t>summary.product_detail</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>MF</t>
+          <t>One-, two-, and three-bedroom residences averaging 856 square feet across 40 buildings …</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -10066,27 +10082,33 @@
         </is>
       </c>
       <c r="F38" s="12" t="n"/>
-      <c r="G38" s="13" t="n"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>the property offers a diversified mix of 
+one-, two-, and three-bedroom residences averaging 856 square 
+feet</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>garden-style multifamily</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -10097,14 +10119,14 @@
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -10114,7 +10136,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -10130,14 +10152,14 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -10147,7 +10169,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -10163,29 +10185,29 @@
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Sample City Residential Holdings LLC</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>p.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -10194,27 +10216,31 @@
         </is>
       </c>
       <c r="F42" s="12" t="n"/>
-      <c r="G42" s="13" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Institutional owner-operator (name withheld)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>withheld</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -10223,27 +10249,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n"/>
-      <c r="G43" s="13" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>505 W Baseline Rd</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -10254,29 +10284,29 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>1400 Example Parkway</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Three-story garden, surface parked</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -10287,29 +10317,29 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Three-story garden, surface parked</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -10320,29 +10350,29 @@
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Number of Stories 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Limited property value (LPV), per the county assessor</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -10353,19 +10383,19 @@
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>What the assessed basis is in this state.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -10386,29 +10416,29 @@
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>How the basis behaves on a sale, with the authority.</t>
+          <t>What the assessed basis is in this state.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -10419,29 +10449,29 @@
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>How the basis behaves on a sale, with the authority.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>249,122</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -10452,29 +10482,29 @@
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -10485,29 +10515,29 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -10518,14 +10548,14 @@
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -10551,56 +10581,52 @@
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline reads the parcel, tax district, assessed value, exemption and billed amount off the county assessor's portal; the demo shows the county's published rate only.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_per_unit_flag</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>OUTSIDE the band (the statement's line per unit): $2,797 per unit a year is outside the…</t>
+          <t>301-04-002K</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.band_check</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n"/>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+          <t>Tax Parcel Number 301-04-002K</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -10610,30 +10636,34 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_evidence</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -10643,34 +10673,30 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.evidence_text</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>summary.state, summary.county</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file.</t>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_year</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -10680,143 +10706,151 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_statement_amount</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>503,391.9</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>the synthetic trailing-twelve statement</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Property Taxes lines</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>t12.rows</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="n"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>239,566.79</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Rent Roll!A:A</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>t12.rows</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>Distinct unit identifiers on the roll.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>p.6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="13" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Counted from the rows of the uploaded rent roll.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>1,981</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Synthetic offering memorandum</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>p.4</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -10825,27 +10859,31 @@
         </is>
       </c>
       <c r="F61" s="12" t="n"/>
-      <c r="G61" s="13" t="n"/>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Y ear Built 1981</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>supply.rings</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>8 entries</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -10856,29 +10894,29 @@
       <c r="F62" s="12" t="n"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>supply.rings</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>8 entries</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Synthetic trailing-twelve income statement</t>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>T-12!C8:N8</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -10889,29 +10927,29 @@
       <c r="F63" s="12" t="n"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Twelve consecutive month-end columns; direction detected from the labels.</t>
+          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>t12.month_labels</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>5 keys</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Synthetic trailing-twelve income statement</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>T-12!O</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -10922,62 +10960,58 @@
       <c r="F64" s="12" t="n"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>The statement's own printed subtotals, kept for the cross-tie.</t>
+          <t>Read from the uploaded statement.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>t12.source_subtotals</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>4 keys</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Synthetic rent roll export</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>header block</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="n"/>
       <c r="G65" s="13" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>trade_out.rows</t>
+          <t>t12.units</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -10988,7 +11022,40 @@
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>0 entries</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Not asked for by the upload demo</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>The upload demo does not ask for a lease trade-out report, so there is no basis for a new-versus-renewal block.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -6973,7 +6973,7 @@
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>The upload demo does not ask for a lease trade-out report, so there is no basis for a new-versus-renewal block.</t>
+          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -9878,7 +9878,7 @@
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
@@ -10136,7 +10136,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -10152,7 +10152,7 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -10185,7 +10185,7 @@
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -10218,7 +10218,7 @@
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Not asked for by the upload demo</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -11055,7 +11055,7 @@
       <c r="F67" s="12" t="n"/>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>The upload demo does not ask for a lease trade-out report, so there is no basis for a new-versus-renewal block.</t>
+          <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>From "Southern Avenue Sample". Pricing is illustrative; see the deal summary for the boundary note.</t>
+          <t>From "505 West". Pricing is illustrative; see the deal summary for the boundary note.</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample</t>
+          <t>505 West</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Institutional owner-operator (name withheld)</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Listing brokerage</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample — as of 2026-08-31</t>
+          <t>505 West — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9758,17 +9758,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Southern Avenue Sample</t>
+          <t>505 West</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Illustrative</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -9779,7 +9779,7 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>The sample's name is illustrative; the asset's real name is withheld.</t>
+          <t>The deal name as the memorandum states it.</t>
         </is>
       </c>
     </row>
@@ -9927,17 +9927,17 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Listing brokerage</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>withheld</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -9948,7 +9948,7 @@
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
@@ -10230,17 +10230,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Institutional owner-operator (name withheld)</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>withheld</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -10251,7 +10251,7 @@
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -3263,7 +3263,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa High School</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -10131,17 +10131,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -10152,7 +10152,7 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
@@ -10164,17 +10164,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -10185,7 +10185,7 @@
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
@@ -10197,17 +10197,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -10218,7 +10218,7 @@
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline looks up the attendance-zone elementary, middle and high school and their public ratings; the demo reads a school name only where the memorandum states one and never rates it.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>garden-style multifamily</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>One-, two-, and three-bedroom residences averaging 856 square feet across 40 buildings on 15.87 acres</t>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet on approximately 15.9 acres</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>expense_per_unit</t>
+          <t>t3_trailing_revenue_annualized</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Each rollup row divided by unit count, blank-guarded so a bad unit count cannot fill the column with errors.</t>
+          <t>Six figures: each of the six most recent months plus the two before it, times four — the trend the T-3 cap rate sits at the end of.</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Per-unit expense check</t>
+          <t>Investment analysis — trailing T-3 revenue series</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -5039,17 +5039,17 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>pct_of_revenue</t>
+          <t>statement_guards</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Each rollup row as a share of total revenue.</t>
+          <t>Four sanity checks on how the statement is printed — contra-revenue sign, expense sign, recoveries inside expense buckets, a subtotal counted with its members — each OK or REVIEW with the lines named.</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Expense ratio check</t>
+          <t>Review flags — not a model input</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
@@ -5081,17 +5081,17 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>breakout_top4</t>
+          <t>expense_per_unit</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>For other income, utility reimbursements, and utilities: the four largest constituent lines plus a Rest row, tying to the rollup.</t>
+          <t>Each rollup row divided by unit count, blank-guarded so a bad unit count cannot fill the column with errors.</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Other-income / utility detail</t>
+          <t>Per-unit expense check</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -5123,27 +5123,27 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>source_subtotal</t>
+          <t>pct_of_revenue</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>A subtotal as printed on the source statement, kept for the cross-tie.</t>
+          <t>Each rollup row as a share of total revenue.</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Trailing-twelve-month income statement</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Expense ratio check</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
@@ -5165,17 +5165,17 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>error_check_difference</t>
+          <t>breakout_top4</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>table</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Our category total less the source's printed subtotal. Anything over a dollar reads REVIEW rather than quietly passing.</t>
+          <t>For other income, utility reimbursements, and utilities: the four largest constituent lines plus a Rest row, tying to the rollup.</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Other-income / utility detail</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -5207,137 +5207,137 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>source_subtotal</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Why the T-12 section is empty, when no trailing-twelve statement was supplied. Twelve months of zeroes would validate and read as a property that earned nothing; a stated reason cannot be mistaken for one.</t>
+          <t>A subtotal as printed on the source statement, kept for the cross-tie.</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
+          <t>Trailing-twelve-month income statement</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>T-12 structure</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>error_check_difference</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Our category total less the source's printed subtotal. Anything over a dollar reads REVIEW rather than quietly passing.</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F128" s="7" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — unit</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="n"/>
-      <c r="C129" s="5" t="n"/>
-      <c r="D129" s="5" t="n"/>
-      <c r="E129" s="5" t="n"/>
-      <c r="F129" s="5" t="n"/>
-      <c r="G129" s="5" t="n"/>
-      <c r="H129" s="5" t="n"/>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
+          <t>T-12 structure</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Why the T-12 section is empty, when no trailing-twelve statement was supplied. Twelve months of zeroes would validate and read as a property that earned nothing; a stated reason cannot be mistaken for one.</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
           <t>Rent roll — unit</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>unit_id</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D130" s="7" t="inlineStr">
-        <is>
-          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll export</t>
-        </is>
-      </c>
-      <c r="F130" s="7" t="inlineStr">
-        <is>
-          <t>Unit list</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H130" s="7" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — unit</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>floor_plan</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Floor-plan code the unit belongs to.</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll export</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>Unit mix</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>3X2B</t>
-        </is>
-      </c>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -5347,17 +5347,17 @@
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>beds</t>
+          <t>unit_id</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms.</t>
+          <t>Unit identifier. The output carries unit IDs only; no tenant-name column exists in the schema.</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Unit mix</t>
+          <t>Unit list</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1001</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>baths</t>
+          <t>floor_plan</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms.</t>
+          <t>Floor-plan code the unit belongs to.</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3X2B</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>sqft</t>
+          <t>beds</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Square footage.</t>
+          <t>Bedrooms.</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>1,444.0</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
@@ -5473,17 +5473,17 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>baths</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Occupied, vacant, or model/down.</t>
+          <t>Bathrooms.</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Unit mix</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>Occupied</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -5515,17 +5515,17 @@
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>lease_start</t>
+          <t>sqft</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
+          <t>Square footage.</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Unit mix</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>1,444.0</t>
         </is>
       </c>
     </row>
@@ -5557,17 +5557,17 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>move_in</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
+          <t>Occupied, vacant, or model/down.</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>2019-09-25</t>
+          <t>Occupied</t>
         </is>
       </c>
     </row>
@@ -5599,27 +5599,27 @@
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>lease_type</t>
+          <t>lease_start</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
+          <t>Lease start. A value the source gave as text stays text — a date that arrives as 'n/a' is not coerced into 1899.</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Rent roll export</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>New-vs-renewal split</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -5641,17 +5641,17 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>in_place_rent</t>
+          <t>move_in</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Contract rent in place.</t>
+          <t>Move-in date. Turnover is counted by move-in, not by lease start.</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>$2,258</t>
+          <t>2019-09-25</t>
         </is>
       </c>
     </row>
@@ -5683,137 +5683,137 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>rent_per_sf</t>
+          <t>lease_type</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>New, Renewal, or blank. Blank means the source could not support a classification — never a guess, never a blend.</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>New-vs-renewal split</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — unit</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>in_place_rent</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>In-place rent divided by square footage.</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>Rent per square foot</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H140" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — plan</t>
-        </is>
-      </c>
-      <c r="B141" s="5" t="n"/>
-      <c r="C141" s="5" t="n"/>
-      <c r="D141" s="5" t="n"/>
-      <c r="E141" s="5" t="n"/>
-      <c r="F141" s="5" t="n"/>
-      <c r="G141" s="5" t="n"/>
-      <c r="H141" s="5" t="n"/>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Contract rent in place.</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>In-place rent</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>$2,258</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
+          <t>Rent roll — unit</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>rent_per_sf</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>In-place rent divided by square footage.</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>Rent per square foot</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
           <t>Rent roll — plan</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>plan_avg_sqft</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>Average square footage for the plan.</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>Unit mix — average SF</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H142" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — plan</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>plan_units</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Units in the plan.</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>Unit mix — count</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="n"/>
+      <c r="G143" s="5" t="n"/>
+      <c r="H143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -5823,17 +5823,17 @@
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>plan_occupied</t>
+          <t>plan_avg_sqft</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>Occupied units in the plan.</t>
+          <t>Average square footage for the plan.</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Occupancy by plan</t>
+          <t>Unit mix — average SF</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>plan_vacant</t>
+          <t>plan_units</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Vacant units in the plan.</t>
+          <t>Units in the plan.</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Occupancy by plan</t>
+          <t>Unit mix — count</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -5907,17 +5907,17 @@
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>plan_avg_in_place_rent</t>
+          <t>plan_occupied</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>Weighted average in-place rent for the plan's occupied units.</t>
+          <t>Occupied units in the plan.</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>In-place rent by plan</t>
+          <t>Occupancy by plan</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_rent</t>
+          <t>plan_vacant</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
+          <t>Vacant units in the plan.</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>New-lease rent evidence</t>
+          <t>Occupancy by plan</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
@@ -5991,17 +5991,17 @@
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_count</t>
+          <t>plan_avg_in_place_rent</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
+          <t>Weighted average in-place rent for the plan's occupied units.</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
-          <t>Sample size</t>
+          <t>In-place rent by plan</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_for_model</t>
+          <t>plan_new_lease_rent</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>Unit-mix market rent</t>
+          <t>New-lease rent evidence</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_basis</t>
+          <t>plan_new_lease_count</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>Which of the two fired, stated per plan.</t>
+          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -6110,102 +6110,102 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="n"/>
-      <c r="C151" s="5" t="n"/>
-      <c r="D151" s="5" t="n"/>
-      <c r="E151" s="5" t="n"/>
-      <c r="F151" s="5" t="n"/>
-      <c r="G151" s="5" t="n"/>
-      <c r="H151" s="5" t="n"/>
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>plan_market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Unit-mix market rent</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>plan_market_rent_basis</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>Which of the two fired, stated per plan.</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
           <t>Rent roll — totals</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>total_units</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>Units on the roll.</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr">
-        <is>
-          <t>Unit count cross-check</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>occupied_units</t>
-        </is>
-      </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D153" s="7" t="inlineStr">
-        <is>
-          <t>Occupied units.</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+      <c r="E153" s="5" t="n"/>
+      <c r="F153" s="5" t="n"/>
+      <c r="G153" s="5" t="n"/>
+      <c r="H153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -6215,17 +6215,17 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>vacant_units</t>
+          <t>reconciliation_verdict</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>Vacant units.</t>
+          <t>PASS, FAIL or NOT CHECKED: the unit count (tolerance 0) and the export's stated market-rent total (tolerance $1) against what the export states, every duplicate row retaining the in-place lease, and no rent-readback mismatch.</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Gate — the pack is partial until PASS</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
@@ -6257,17 +6257,17 @@
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>occupancy</t>
+          <t>total_units</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Occupied over total.</t>
+          <t>Units on the roll.</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="F155" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Unit count cross-check</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>vacancy</t>
+          <t>occupied_units</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>One less occupancy. The physical-vacancy input.</t>
+          <t>Occupied units.</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>wavg_in_place_rent</t>
+          <t>vacant_units</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted in-place rent across the property.</t>
+          <t>Vacant units.</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
@@ -6383,17 +6383,17 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>wavg_market_rent_for_model</t>
+          <t>occupancy</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted market rent for model across the property.</t>
+          <t>Occupied over total.</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Market rent</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>annualized_turnover</t>
+          <t>vacancy</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Move-ins inside the lookback window, annualized against unit count.</t>
+          <t>One less occupancy. The physical-vacancy input.</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Turnover assumption</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
@@ -6467,27 +6467,27 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>lookback_months</t>
+          <t>wavg_in_place_rent</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
+          <t>Unit-weighted in-place rent across the property.</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6509,27 +6509,27 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>new_tenant_tolerance_days</t>
+          <t>wavg_market_rent_for_model</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
+          <t>Unit-weighted market rent for model across the property.</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market rent</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6551,17 +6551,17 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>annualized_turnover</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+          <t>Move-ins inside the lookback window, annualized against unit count.</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Turnover assumption</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
@@ -6593,27 +6593,27 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>roll_as_of</t>
+          <t>lookback_months</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>As-of date of the roll. Every window is measured from here.</t>
+          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Analysis date</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
@@ -6623,33 +6623,61 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="5" t="n"/>
-      <c r="D164" s="5" t="n"/>
-      <c r="E164" s="5" t="n"/>
-      <c r="F164" s="5" t="n"/>
-      <c r="G164" s="5" t="n"/>
-      <c r="H164" s="5" t="n"/>
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>new_tenant_tolerance_days</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>Supplied by the operator</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>Trade-out</t>
+          <t>Rent roll — totals</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>cohort</t>
+          <t>absent_reason</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -6659,22 +6687,22 @@
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>New, Renewal, or First generation.</t>
+          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>Lease trade-out report</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>New-vs-renewal growth evidence</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
@@ -6686,86 +6714,58 @@
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>roll_as_of</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>As-of date of the roll. Every window is measured from here.</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>Analysis date</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
           <t>Trade-out</t>
         </is>
       </c>
-      <c r="B166" s="6" t="inlineStr">
-        <is>
-          <t>cohort_leases</t>
-        </is>
-      </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D166" s="7" t="inlineStr">
-        <is>
-          <t>Leases in the cohort.</t>
-        </is>
-      </c>
-      <c r="E166" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>Sample size</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="inlineStr">
-        <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
-        </is>
-      </c>
-      <c r="H166" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>cohort_prior_rent</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>Average rent before the trade.</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>Prior rent</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr">
-        <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="n"/>
+      <c r="G167" s="5" t="n"/>
+      <c r="H167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
@@ -6775,17 +6775,17 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_gross</t>
+          <t>cohort</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>Average new rent before concessions.</t>
+          <t>New, Renewal, or First generation.</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Gross trade-out</t>
+          <t>New-vs-renewal growth evidence</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_effective</t>
+          <t>cohort_leases</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
+          <t>Leases in the cohort.</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Effective trade-out</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
@@ -6859,32 +6859,32 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>cohort_prior_rent</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Average rent before the trade.</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Prior rent</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>cohort_new_rent_gross</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Average new rent before concessions.</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Gross trade-out</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H171" s="7" t="inlineStr">
@@ -6943,83 +6943,111 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>cohort_new_rent_effective</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
+          <t>Lease trade-out report</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>Effective trade-out</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>cohort_gross_change_pct</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>Gross change over prior rent.</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>Reference only — not a model input</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
-        </is>
-      </c>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="n"/>
-      <c r="C173" s="5" t="n"/>
-      <c r="D173" s="5" t="n"/>
-      <c r="E173" s="5" t="n"/>
-      <c r="F173" s="5" t="n"/>
-      <c r="G173" s="5" t="n"/>
-      <c r="H173" s="5" t="n"/>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>Rent growth evidence</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>Comps</t>
+          <t>Trade-out</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>comp_community</t>
+          <t>cohort_effective_change_pct</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>Comparable community name.</t>
+          <t>Effective change over prior rent.</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Rent growth evidence</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
@@ -7029,93 +7057,65 @@
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
-          <t>Saltera Apartments</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>comp_distance_mi</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>Straight-line distance from the subject.</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F175" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>comp_floor_plan</t>
-        </is>
-      </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
-        </is>
-      </c>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="5" t="n"/>
+      <c r="D176" s="5" t="n"/>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
+      <c r="H176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -7125,22 +7125,22 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>comp_tier</t>
+          <t>comp_community</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
+          <t>Comparable community name.</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Saltera Apartments</t>
         </is>
       </c>
     </row>
@@ -7167,22 +7167,22 @@
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D178" s="7" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>1,984</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built_source</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>vendor note on the tracked community record, via the market-report service</t>
+          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
         </is>
       </c>
     </row>
@@ -7251,27 +7251,27 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>nearby_community</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>Trails at Harris</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>nearby_address</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Its address, so the reader can place it.</t>
+          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
+          <t>1,984</t>
         </is>
       </c>
     </row>
@@ -7335,27 +7335,27 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>nearby_distance_mi</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject.</t>
+          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>vendor note on the tracked community record, via the market-report service</t>
         </is>
       </c>
     </row>
@@ -7377,17 +7377,17 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>nearby_units</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one.</t>
+          <t>A tracked community inside the radius that is NOT a comp.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>Trails at Harris</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>nearby_reason</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
+          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
         </is>
       </c>
     </row>
@@ -7461,17 +7461,17 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>compset_vintage_footnote</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Vintage filter: +/-10 years of the subject's year built.</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -7503,17 +7503,17 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>Unit count where the registry has one.</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -7545,27 +7545,27 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
         </is>
       </c>
     </row>
@@ -7587,27 +7587,27 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>Vintage filter: +/-10 years of the subject's year built.</t>
         </is>
       </c>
     </row>
@@ -7629,17 +7629,17 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -7671,17 +7671,17 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7713,27 +7713,27 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>688.0</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -7765,17 +7765,17 @@
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,047</t>
         </is>
       </c>
     </row>
@@ -7797,17 +7797,17 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -7839,27 +7839,27 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>$1,047</t>
         </is>
       </c>
     </row>
@@ -7881,27 +7881,27 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
@@ -7965,27 +7965,27 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -8007,73 +8007,101 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>subject_vs_compset_spread</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>Subject market rent over comp-set net effective, less one.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
+          <t>Operator's own weekly rent scrape</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>compset_avg_asking</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>Average asking rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F198" s="7" t="inlineStr">
-        <is>
-          <t>Rent positioning</t>
-        </is>
-      </c>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B199" s="5" t="n"/>
-      <c r="C199" s="5" t="n"/>
-      <c r="D199" s="5" t="n"/>
-      <c r="E199" s="5" t="n"/>
-      <c r="F199" s="5" t="n"/>
-      <c r="G199" s="5" t="n"/>
-      <c r="H199" s="5" t="n"/>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>Demand</t>
+          <t>Comps</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>demand_ring</t>
+          <t>compset_avg_net_effective</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
+          <t>Average net effective rent across the comp set.</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -8083,7 +8111,7 @@
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Market rent benchmark</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
@@ -8093,93 +8121,65 @@
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>1 mi</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>subject_vs_compset_spread</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Subject market rent over comp-set net effective, less one.</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>Rent positioning</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B201" s="6" t="inlineStr">
-        <is>
-          <t>demand_population</t>
-        </is>
-      </c>
-      <c r="C201" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D201" s="7" t="inlineStr">
-        <is>
-          <t>Population in the ring.</t>
-        </is>
-      </c>
-      <c r="E201" s="6" t="inlineStr">
-        <is>
-          <t>Public demographic data</t>
-        </is>
-      </c>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H201" s="7" t="inlineStr">
-        <is>
-          <t>20,297</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="6" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>demand_households</t>
-        </is>
-      </c>
-      <c r="C202" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D202" s="7" t="inlineStr">
-        <is>
-          <t>Households in the ring.</t>
-        </is>
-      </c>
-      <c r="E202" s="6" t="inlineStr">
-        <is>
-          <t>Public demographic data</t>
-        </is>
-      </c>
-      <c r="F202" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G202" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H202" s="7" t="inlineStr">
-        <is>
-          <t>7,711</t>
-        </is>
-      </c>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
+      <c r="F202" s="5" t="n"/>
+      <c r="G202" s="5" t="n"/>
+      <c r="H202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -8189,27 +8189,27 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>$79,735</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="D204" s="7" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>5,239</t>
+          <t>20,297</t>
         </is>
       </c>
     </row>
@@ -8273,17 +8273,17 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>7,711</t>
         </is>
       </c>
     </row>
@@ -8315,17 +8315,17 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>demand_renter_share</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
-          <t>Share of ring households that rent.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>Demand context</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
@@ -8345,53 +8345,81 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>$79,735</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B207" s="5" t="n"/>
-      <c r="C207" s="5" t="n"/>
-      <c r="D207" s="5" t="n"/>
-      <c r="E207" s="5" t="n"/>
-      <c r="F207" s="5" t="n"/>
-      <c r="G207" s="5" t="n"/>
-      <c r="H207" s="5" t="n"/>
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>demand_jobs</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>Jobs located in the ring.</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H207" s="7" t="inlineStr">
+        <is>
+          <t>5,239</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>Supply</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>supply_ring</t>
+          <t>demand_pop_growth_5yr</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>Ring the supply row describes.</t>
+          <t>Five-year population growth in the ring.</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public demographic data</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Growth assumption evidence</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
@@ -8401,93 +8429,65 @@
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>1 mi</t>
+          <t>-2.0%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>demand_renter_share</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>Share of ring households that rent.</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>Demand context</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>43.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>supply_stage</t>
-        </is>
-      </c>
-      <c r="C209" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D209" s="7" t="inlineStr">
-        <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
-        <is>
-          <t>Public permit / entitlement records</t>
-        </is>
-      </c>
-      <c r="F209" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G209" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H209" s="7" t="inlineStr">
-        <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="6" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B210" s="6" t="inlineStr">
-        <is>
-          <t>supply_projects</t>
-        </is>
-      </c>
-      <c r="C210" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D210" s="7" t="inlineStr">
-        <is>
-          <t>Projects at that ring and stage.</t>
-        </is>
-      </c>
-      <c r="E210" s="6" t="inlineStr">
-        <is>
-          <t>Public permit / entitlement records</t>
-        </is>
-      </c>
-      <c r="F210" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G210" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H210" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="5" t="n"/>
+      <c r="F210" s="5" t="n"/>
+      <c r="G210" s="5" t="n"/>
+      <c r="H210" s="5" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -8497,27 +8497,27 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>supply_ring</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Ring the supply row describes.</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -8539,22 +8539,22 @@
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>supply_stage</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -8581,27 +8581,27 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>supply_pct_of_ring_stock</t>
+          <t>supply_projects</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
+          <t>Projects at that ring and stage.</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>Supply pressure</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
@@ -8611,53 +8611,81 @@
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="n"/>
-      <c r="C214" s="5" t="n"/>
-      <c r="D214" s="5" t="n"/>
-      <c r="E214" s="5" t="n"/>
-      <c r="F214" s="5" t="n"/>
-      <c r="G214" s="5" t="n"/>
-      <c r="H214" s="5" t="n"/>
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>supply_units</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>Units at that ring and stage.</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply / absorption</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H214" s="7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>om_rent_comp_community</t>
+          <t>supply_ring_total_units</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
+          <t>All pipeline units in the ring across stages.</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>Rent comps (broker-stated)</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
@@ -8674,86 +8702,58 @@
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>supply_pct_of_ring_stock</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>Supply pressure</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H216" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
           <t>OM comparables</t>
         </is>
       </c>
-      <c r="B216" s="6" t="inlineStr">
-        <is>
-          <t>om_rent_comp_distance_mi</t>
-        </is>
-      </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D216" s="7" t="inlineStr">
-        <is>
-          <t>Distance from the subject as the memorandum states it.</t>
-        </is>
-      </c>
-      <c r="E216" s="6" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F216" s="7" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G216" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H216" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="6" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B217" s="6" t="inlineStr">
-        <is>
-          <t>om_rent_comp_rent</t>
-        </is>
-      </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D217" s="7" t="inlineStr">
-        <is>
-          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
-        </is>
-      </c>
-      <c r="E217" s="6" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F217" s="7" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G217" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H217" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="5" t="n"/>
+      <c r="F217" s="5" t="n"/>
+      <c r="G217" s="5" t="n"/>
+      <c r="H217" s="5" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_property</t>
+          <t>om_rent_comp_community</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price</t>
+          <t>om_rent_comp_distance_mi</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>The stated sale price.</t>
+          <t>Distance from the subject as the memorandum states it.</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price_per_unit</t>
+          <t>om_rent_comp_rent</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>The stated price per unit.</t>
+          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
@@ -8889,17 +8889,17 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_cap_rate</t>
+          <t>om_sale_comp_property</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>The stated cap rate, as a fraction.</t>
+          <t>A whole-community sale comparable the memorandum cites, by name.</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
@@ -8931,35 +8931,161 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
+          <t>om_sale_comp_price</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>The stated sale price.</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_price_per_unit</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>The stated price per unit.</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H223" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_cap_rate</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>The stated cap rate, as a fraction.</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H224" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
           <t>om_sale_comp_date</t>
         </is>
       </c>
-      <c r="C222" s="6" t="inlineStr">
+      <c r="C225" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D222" s="7" t="inlineStr">
+      <c r="D225" s="7" t="inlineStr">
         <is>
           <t>The sale date as written.</t>
         </is>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="E225" s="6" t="inlineStr">
         <is>
           <t>Offering memorandum / marketing package</t>
         </is>
       </c>
-      <c r="F222" s="7" t="inlineStr">
+      <c r="F225" s="7" t="inlineStr">
         <is>
           <t>Sale comps (institutional)</t>
         </is>
       </c>
-      <c r="G222" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H222" s="7" t="inlineStr">
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10063,7 +10189,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>One-, two-, and three-bedroom residences averaging 856 square feet across 40 buildings …</t>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -10098,7 +10224,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>garden-style multifamily</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7">
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>From "505 West". Pricing is illustrative; see the deal summary for the boundary note.</t>
+          <t>From "Sample Mesa Apt". Pricing is illustrative; see the deal summary for the boundary note.</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>505 West</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). Tier 3 is identity-only and carries no rent.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp.</t>
+          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The column that answers 'why isn't the property across the street in your comp set?'.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
@@ -8742,48 +8742,76 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="n"/>
-      <c r="C217" s="5" t="n"/>
-      <c r="D217" s="5" t="n"/>
-      <c r="E217" s="5" t="n"/>
-      <c r="F217" s="5" t="n"/>
-      <c r="G217" s="5" t="n"/>
-      <c r="H217" s="5" t="n"/>
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>supply_project_name</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="inlineStr">
+        <is>
+          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H217" s="7" t="inlineStr">
+        <is>
+          <t>Reed Park Residences</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>om_rent_comp_community</t>
+          <t>supply_project_miles</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
+          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>Rent comps (broker-stated)</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
@@ -8793,39 +8821,39 @@
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>om_rent_comp_distance_mi</t>
+          <t>supply_project_stage</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject as the memorandum states it.</t>
+          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>Rent comps (broker-stated)</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
@@ -8835,39 +8863,39 @@
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>om_rent_comp_rent</t>
+          <t>supply_project_units</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
+          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>Rent comps (broker-stated)</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
@@ -8877,19 +8905,19 @@
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_property</t>
+          <t>supply_project_product</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
@@ -8899,17 +8927,17 @@
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+          <t>Product the pipeline records for the development.</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
@@ -8919,39 +8947,39 @@
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>multifamily</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price</t>
+          <t>supply_project_address</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>The stated sale price.</t>
+          <t>Street address where a layer carried one.</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
@@ -8968,32 +8996,32 @@
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price_per_unit</t>
+          <t>supply_project_city</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>The stated price per unit.</t>
+          <t>City where a layer carried one.</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
@@ -9010,32 +9038,32 @@
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>OM comparables</t>
+          <t>Supply</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_cap_rate</t>
+          <t>supply_project_acres</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>The stated cap rate, as a fraction.</t>
+          <t>Site acreage where a layer carried one.</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Offering memorandum / marketing package</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
@@ -9045,47 +9073,523 @@
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>supply_project_developer</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="inlineStr">
+        <is>
+          <t>Developer where a layer named one.</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>supply_project_filed</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>Earliest filing date across the layers the development appears on.</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>supply_project_latest</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>Latest activity date across those layers.</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H227" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>supply_project_layers</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>The pipeline layers the development appeared on. Layers are lifecycle views of the same market, so one development can appear on several and is counted once.</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H228" s="7" t="inlineStr">
+        <is>
+          <t>1 entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
           <t>OM comparables</t>
         </is>
       </c>
-      <c r="B225" s="6" t="inlineStr">
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="5" t="n"/>
+      <c r="F229" s="5" t="n"/>
+      <c r="G229" s="5" t="n"/>
+      <c r="H229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>om_rent_comp_community</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>Rent comps (broker-stated)</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>om_rent_comp_distance_mi</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="inlineStr">
+        <is>
+          <t>Distance from the subject as the memorandum states it.</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>Rent comps (broker-stated)</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>om_rent_comp_rent</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>Rent comps (broker-stated)</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H232" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_property</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D233" s="7" t="inlineStr">
+        <is>
+          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H233" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_price</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>The stated sale price.</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H234" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_price_per_unit</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D235" s="7" t="inlineStr">
+        <is>
+          <t>The stated price per unit.</t>
+        </is>
+      </c>
+      <c r="E235" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H235" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_cap_rate</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>The stated cap rate, as a fraction.</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H236" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
         <is>
           <t>om_sale_comp_date</t>
         </is>
       </c>
-      <c r="C225" s="6" t="inlineStr">
+      <c r="C237" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D225" s="7" t="inlineStr">
+      <c r="D237" s="7" t="inlineStr">
         <is>
           <t>The sale date as written.</t>
         </is>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E237" s="6" t="inlineStr">
         <is>
           <t>Offering memorandum / marketing package</t>
         </is>
       </c>
-      <c r="F225" s="7" t="inlineStr">
+      <c r="F237" s="7" t="inlineStr">
         <is>
           <t>Sale comps (institutional)</t>
         </is>
       </c>
-      <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H225" s="7" t="inlineStr">
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H237" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9102,7 +9606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9124,7 +9628,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>505 West — as of 2026-08-31</t>
+          <t>Sample Mesa Apt — as of 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9656,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -9303,7 +9807,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Every community the service returned that is not a detail row, with the reason.</t>
+          <t>Every community the service returned that is not a detail row, with the reason. Carried in the interchange file; not shown as a table.</t>
         </is>
       </c>
     </row>
@@ -9884,17 +10388,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>505 West</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -9905,7 +10409,7 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>The deal name as the memorandum states it.</t>
+          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
         </is>
       </c>
     </row>
@@ -11027,55 +11531,59 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
+          <t>supply.projects</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>32 entries</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
           <t>supply.rings</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>8 entries</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>POST /report (format json)</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="n"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
+          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>supply.rings</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>8 entries</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -11086,19 +11594,19 @@
       <c r="F64" s="12" t="n"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Read from the uploaded statement.</t>
+          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>t12.month_labels</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>4 keys</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -11108,7 +11616,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>header block</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -11117,17 +11625,21 @@
         </is>
       </c>
       <c r="F65" s="12" t="n"/>
-      <c r="G65" s="13" t="n"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>t12.source_subtotals</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>4 keys</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -11137,7 +11649,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>header block</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -11146,31 +11658,27 @@
         </is>
       </c>
       <c r="F66" s="12" t="n"/>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>Read from the uploaded statement.</t>
-        </is>
-      </c>
+      <c r="G66" s="13" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>trade_out.rows</t>
+          <t>t12.units</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -11180,6 +11688,39 @@
       </c>
       <c r="F67" s="12" t="n"/>
       <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>0 entries</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Internal pipeline only</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>The rent to underwrite: new-lease average where the plan has new leases in the lookback window, otherwise in-place. Never a blend of new and renewal.</t>
+          <t>The rent to underwrite: new move-in rent (residents who moved in inside the lookback window, by move-in date) where the plan has one, otherwise in-place. Requires a usable lease start AND move-in date on the roll; without either it is in-place outright. Never a blend of new and renewal.</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_rent</t>
+          <t>plan_signed_rent</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
+          <t>Average rent on every priced, CLASSIFIED lease start (new, renewal or month-to-month) inside the lookback window; a lease the roll cannot classify is left out, so this can undercount. Context only: a blend never feeds the model.</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
-          <t>New-lease rent evidence</t>
+          <t>Leases signed</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>plan_new_lease_count</t>
+          <t>plan_signed_count</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
+          <t>How many leases were signed in the window. n/a where the roll has no usable lease-start or move-in date.</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_for_model</t>
+          <t>plan_movein_rent</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+          <t>Average rent of residents whose move-in date falls inside the lookback window, whatever their lease type.</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Unit-mix market rent</t>
+          <t>New move-in rent evidence</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>plan_market_rent_basis</t>
+          <t>plan_movein_count</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Which of the two fired, stated per plan.</t>
+          <t>How many move-ins the average rests on. A thin count is visible rather than implied.</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
@@ -6194,102 +6194,102 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B153" s="5" t="n"/>
-      <c r="C153" s="5" t="n"/>
-      <c r="D153" s="5" t="n"/>
-      <c r="E153" s="5" t="n"/>
-      <c r="F153" s="5" t="n"/>
-      <c r="G153" s="5" t="n"/>
-      <c r="H153" s="5" t="n"/>
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>plan_market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>The plan's rent to underwrite: new move-in rent where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>Unit-mix market rent</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>plan_market_rent_basis</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>Which of the two fired, stated per plan.</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
           <t>Rent roll — totals</t>
         </is>
       </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>reconciliation_verdict</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D154" s="7" t="inlineStr">
-        <is>
-          <t>PASS, FAIL or NOT CHECKED: the unit count (tolerance 0) and the export's stated market-rent total (tolerance $1) against what the export states, every duplicate row retaining the in-place lease, and no rent-readback mismatch.</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F154" s="7" t="inlineStr">
-        <is>
-          <t>Gate — the pack is partial until PASS</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>total_units</t>
-        </is>
-      </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D155" s="7" t="inlineStr">
-        <is>
-          <t>Units on the roll.</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>Unit count cross-check</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H155" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="n"/>
+      <c r="G155" s="5" t="n"/>
+      <c r="H155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>occupied_units</t>
+          <t>reconciliation_verdict</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>Occupied units.</t>
+          <t>PASS, FAIL or NOT CHECKED: the unit count (tolerance 0) and the export's stated market-rent total (tolerance $1) against what the export states, every duplicate row retaining the in-place lease, and no rent-readback mismatch.</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="F156" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Gate — the pack is partial until PASS</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>vacant_units</t>
+          <t>total_units</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Vacant units.</t>
+          <t>Units on the roll.</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Unit count cross-check</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
@@ -6383,17 +6383,17 @@
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>occupancy</t>
+          <t>occupied_units</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Occupied over total.</t>
+          <t>Occupied units.</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
@@ -6425,17 +6425,17 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>vacancy</t>
+          <t>vacant_units</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>One less occupancy. The physical-vacancy input.</t>
+          <t>Vacant units.</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="F159" s="7" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
@@ -6467,17 +6467,17 @@
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>wavg_in_place_rent</t>
+          <t>occupancy</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted in-place rent across the property.</t>
+          <t>Occupied over total.</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="F160" s="7" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
@@ -6509,17 +6509,17 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>wavg_market_rent_for_model</t>
+          <t>vacancy</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted market rent for model across the property.</t>
+          <t>One less occupancy. The physical-vacancy input.</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Market rent</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
@@ -6551,17 +6551,17 @@
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>annualized_turnover</t>
+          <t>wavg_in_place_rent</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>Move-ins inside the lookback window, annualized against unit count.</t>
+          <t>Unit-weighted in-place rent across the property.</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Turnover assumption</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
@@ -6593,27 +6593,27 @@
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>lookback_months</t>
+          <t>wavg_market_rent_for_model</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
+          <t>Unit-weighted market rent for model across the property.</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market rent</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6635,27 +6635,27 @@
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>new_tenant_tolerance_days</t>
+          <t>annualized_turnover</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
+          <t>Move-ins inside the lookback window, annualized against unit count.</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Turnover assumption</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6677,22 +6677,22 @@
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>lookback_months</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+          <t>Length of the move-in and lease-signed window, measured back from the roll's as-of date.</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -6719,27 +6719,27 @@
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>roll_as_of</t>
+          <t>new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>As-of date of the roll. Every window is measured from here.</t>
+          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Analysis date</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
@@ -6749,107 +6749,107 @@
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="n"/>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="5" t="n"/>
-      <c r="E167" s="5" t="n"/>
-      <c r="F167" s="5" t="n"/>
-      <c r="G167" s="5" t="n"/>
-      <c r="H167" s="5" t="n"/>
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>roll_as_of</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>As-of date of the roll. Every window is measured from here.</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>Analysis date</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
           <t>Trade-out</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>New, Renewal, or First generation.</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>New-vs-renewal growth evidence</t>
-        </is>
-      </c>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>cohort_leases</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Leases in the cohort.</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>Sample size</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
+      <c r="E169" s="5" t="n"/>
+      <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
@@ -6859,17 +6859,17 @@
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>cohort_prior_rent</t>
+          <t>cohort</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>Average rent before the trade.</t>
+          <t>New, Renewal, or First generation.</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>Prior rent</t>
+          <t>New-vs-renewal growth evidence</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_gross</t>
+          <t>cohort_leases</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Average new rent before concessions.</t>
+          <t>Leases in the cohort.</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Gross trade-out</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>cohort_new_rent_effective</t>
+          <t>cohort_prior_rent</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
-          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
+          <t>Average rent before the trade.</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Effective trade-out</t>
+          <t>Prior rent</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
@@ -6985,32 +6985,32 @@
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>cohort_new_rent_gross</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Average new rent before concessions.</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Gross trade-out</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H173" s="7" t="inlineStr">
@@ -7027,32 +7027,32 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>cohort_new_rent_effective</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D174" s="7" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Effective trade-out</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H174" s="7" t="inlineStr">
@@ -7069,17 +7069,17 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>cohort_gross_change_pct</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+          <t>Gross change over prior rent.</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -7089,117 +7089,117 @@
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Rent growth evidence</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="n"/>
-      <c r="C176" s="5" t="n"/>
-      <c r="D176" s="5" t="n"/>
-      <c r="E176" s="5" t="n"/>
-      <c r="F176" s="5" t="n"/>
-      <c r="G176" s="5" t="n"/>
-      <c r="H176" s="5" t="n"/>
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>cohort_effective_change_pct</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>Effective change over prior rent.</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>Rent growth evidence</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H176" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>comp_community</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D177" s="7" t="inlineStr">
-        <is>
-          <t>Comparable community name.</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr">
-        <is>
-          <t>Saltera Apartments</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
-        <is>
-          <t>comp_distance_mi</t>
-        </is>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
-          <t>Straight-line distance from the subject.</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="n"/>
+      <c r="E178" s="5" t="n"/>
+      <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5" t="n"/>
+      <c r="H178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>comp_floor_plan</t>
+          <t>comp_community</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
+          <t>Comparable community name.</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>Saltera Apartments</t>
         </is>
       </c>
     </row>
@@ -7251,17 +7251,17 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>comp_tier</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>1,984</t>
+          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
         </is>
       </c>
     </row>
@@ -7335,27 +7335,27 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built_source</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>vendor note on the tracked community record, via the market-report service</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7377,17 +7377,17 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>nearby_community</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
+          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>Trails at Harris</t>
+          <t>1,984</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>nearby_address</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>Its address, so the reader can place it.</t>
+          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
+          <t>vendor note on the tracked community record, via the market-report service</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>nearby_distance_mi</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject.</t>
+          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>Trails at Harris</t>
         </is>
       </c>
     </row>
@@ -7503,17 +7503,17 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>nearby_units</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
         </is>
       </c>
     </row>
@@ -7545,17 +7545,17 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>nearby_reason</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -7587,27 +7587,27 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>compset_vintage_footnote</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
+          <t>Unit count where the registry has one.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>Vintage filter: +/-10 years of the subject's year built.</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -7629,27 +7629,27 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
         </is>
       </c>
     </row>
@@ -7671,27 +7671,27 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Vintage filter: +/-10 years of the subject's year built.</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -7755,17 +7755,17 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7797,17 +7797,17 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>688.0</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,047</t>
         </is>
       </c>
     </row>
@@ -7965,27 +7965,27 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8007,17 +8007,17 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8049,27 +8049,27 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -8091,27 +8091,27 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
@@ -8133,17 +8133,17 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>subject_vs_compset_spread</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Subject market rent over comp-set net effective, less one.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>Rent positioning</t>
+          <t>Market rent benchmark</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
@@ -8168,102 +8168,102 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B202" s="5" t="n"/>
-      <c r="C202" s="5" t="n"/>
-      <c r="D202" s="5" t="n"/>
-      <c r="E202" s="5" t="n"/>
-      <c r="F202" s="5" t="n"/>
-      <c r="G202" s="5" t="n"/>
-      <c r="H202" s="5" t="n"/>
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>subject_vs_compset_spread</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Subject market rent over comp-set net effective, less one.</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>Rent positioning</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>demand_ring</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D203" s="7" t="inlineStr">
-        <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F203" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G203" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H203" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>demand_population</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D204" s="7" t="inlineStr">
-        <is>
-          <t>Population in the ring.</t>
-        </is>
-      </c>
-      <c r="E204" s="6" t="inlineStr">
-        <is>
-          <t>Public demographic data</t>
-        </is>
-      </c>
-      <c r="F204" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G204" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H204" s="7" t="inlineStr">
-        <is>
-          <t>20,297</t>
-        </is>
-      </c>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="5" t="n"/>
+      <c r="F204" s="5" t="n"/>
+      <c r="G204" s="5" t="n"/>
+      <c r="H204" s="5" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
@@ -8273,22 +8273,22 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>7,711</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -8315,17 +8315,17 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>$79,735</t>
+          <t>20,297</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>5,239</t>
+          <t>7,711</t>
         </is>
       </c>
     </row>
@@ -8399,17 +8399,17 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>$79,735</t>
         </is>
       </c>
     </row>
@@ -8441,137 +8441,137 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>demand_renter_share</t>
+          <t>demand_jobs</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>Jobs located in the ring.</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>5,239</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D209" s="7" t="inlineStr">
-        <is>
-          <t>Share of ring households that rent.</t>
-        </is>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
         <is>
           <t>Public demographic data</t>
         </is>
       </c>
-      <c r="F209" s="7" t="inlineStr">
-        <is>
-          <t>Demand context</t>
-        </is>
-      </c>
-      <c r="G209" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H209" s="7" t="inlineStr">
-        <is>
-          <t>43.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="5" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B210" s="5" t="n"/>
-      <c r="C210" s="5" t="n"/>
-      <c r="D210" s="5" t="n"/>
-      <c r="E210" s="5" t="n"/>
-      <c r="F210" s="5" t="n"/>
-      <c r="G210" s="5" t="n"/>
-      <c r="H210" s="5" t="n"/>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>demand_renter_share</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>Share of ring households that rent.</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>Demand context</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>43.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>supply_ring</t>
-        </is>
-      </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D211" s="7" t="inlineStr">
-        <is>
-          <t>Ring the supply row describes.</t>
-        </is>
-      </c>
-      <c r="E211" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G211" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H211" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
-        <is>
-          <t>supply_stage</t>
-        </is>
-      </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D212" s="7" t="inlineStr">
-        <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>Public permit / entitlement records</t>
-        </is>
-      </c>
-      <c r="F212" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G212" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H212" s="7" t="inlineStr">
-        <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
+      <c r="F212" s="5" t="n"/>
+      <c r="G212" s="5" t="n"/>
+      <c r="H212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -8581,22 +8581,22 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>supply_ring</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>Ring the supply row describes.</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -8623,17 +8623,17 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>supply_stage</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>supply_projects</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Projects at that ring and stage.</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8707,27 +8707,27 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>supply_pct_of_ring_stock</t>
+          <t>supply_units</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
+          <t>Units at that ring and stage.</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>Supply pressure</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -8749,22 +8749,22 @@
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>supply_project_name</t>
+          <t>supply_ring_total_units</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
+          <t>All pipeline units in the ring across stages.</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>Reed Park Residences</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8791,17 +8791,17 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>supply_project_miles</t>
+          <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
+          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Supply pressure</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>supply_project_stage</t>
+          <t>supply_project_name</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
+          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Reed Park Residences</t>
         </is>
       </c>
     </row>
@@ -8875,27 +8875,27 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>supply_project_units</t>
+          <t>supply_project_miles</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
+          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>supply_project_product</t>
+          <t>supply_project_stage</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Product the pipeline records for the development.</t>
+          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -8959,17 +8959,17 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>supply_project_address</t>
+          <t>supply_project_units</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>Street address where a layer carried one.</t>
+          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>supply_project_city</t>
+          <t>supply_project_product</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>City where a layer carried one.</t>
+          <t>Product the pipeline records for the development.</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>multifamily</t>
         </is>
       </c>
     </row>
@@ -9043,17 +9043,17 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>supply_project_acres</t>
+          <t>supply_project_address</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>Site acreage where a layer carried one.</t>
+          <t>Street address where a layer carried one.</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>supply_project_developer</t>
+          <t>supply_project_city</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>Developer where a layer named one.</t>
+          <t>City where a layer carried one.</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
@@ -9127,17 +9127,17 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>supply_project_filed</t>
+          <t>supply_project_acres</t>
         </is>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D226" s="7" t="inlineStr">
         <is>
-          <t>Earliest filing date across the layers the development appears on.</t>
+          <t>Site acreage where a layer carried one.</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="H226" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
@@ -9169,17 +9169,17 @@
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>supply_project_latest</t>
+          <t>supply_project_developer</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>Latest activity date across those layers.</t>
+          <t>Developer where a layer named one.</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9211,17 +9211,17 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>supply_project_layers</t>
+          <t>supply_project_filed</t>
         </is>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D228" s="7" t="inlineStr">
         <is>
-          <t>The pipeline layers the development appeared on. Layers are lifecycle views of the same market, so one development can appear on several and is counted once.</t>
+          <t>Earliest filing date across the layers the development appears on.</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="F228" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G228" s="7" t="inlineStr">
@@ -9241,107 +9241,107 @@
       </c>
       <c r="H228" s="7" t="inlineStr">
         <is>
-          <t>1 entries</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B229" s="5" t="n"/>
-      <c r="C229" s="5" t="n"/>
-      <c r="D229" s="5" t="n"/>
-      <c r="E229" s="5" t="n"/>
-      <c r="F229" s="5" t="n"/>
-      <c r="G229" s="5" t="n"/>
-      <c r="H229" s="5" t="n"/>
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>supply_project_latest</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D229" s="7" t="inlineStr">
+        <is>
+          <t>Latest activity date across those layers.</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H229" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>supply_project_layers</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>The pipeline layers the development appeared on. Layers are lifecycle views of the same market, so one development can appear on several and is counted once.</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>1 entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
           <t>OM comparables</t>
         </is>
       </c>
-      <c r="B230" s="6" t="inlineStr">
-        <is>
-          <t>om_rent_comp_community</t>
-        </is>
-      </c>
-      <c r="C230" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D230" s="7" t="inlineStr">
-        <is>
-          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
-        </is>
-      </c>
-      <c r="E230" s="6" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F230" s="7" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G230" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H230" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="6" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B231" s="6" t="inlineStr">
-        <is>
-          <t>om_rent_comp_distance_mi</t>
-        </is>
-      </c>
-      <c r="C231" s="6" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D231" s="7" t="inlineStr">
-        <is>
-          <t>Distance from the subject as the memorandum states it.</t>
-        </is>
-      </c>
-      <c r="E231" s="6" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G231" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H231" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="5" t="n"/>
+      <c r="F231" s="5" t="n"/>
+      <c r="G231" s="5" t="n"/>
+      <c r="H231" s="5" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -9351,17 +9351,17 @@
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>om_rent_comp_rent</t>
+          <t>om_rent_comp_community</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D232" s="7" t="inlineStr">
         <is>
-          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
+          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -9393,17 +9393,17 @@
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_property</t>
+          <t>om_rent_comp_distance_mi</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+          <t>Distance from the subject as the memorandum states it.</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="F233" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G233" s="7" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price</t>
+          <t>om_rent_comp_rent</t>
         </is>
       </c>
       <c r="C234" s="6" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="D234" s="7" t="inlineStr">
         <is>
-          <t>The stated sale price.</t>
+          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F234" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G234" s="7" t="inlineStr">
@@ -9477,17 +9477,17 @@
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price_per_unit</t>
+          <t>om_sale_comp_property</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>The stated price per unit.</t>
+          <t>A whole-community sale comparable the memorandum cites, by name.</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
@@ -9519,17 +9519,17 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_cap_rate</t>
+          <t>om_sale_comp_price</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
-          <t>The stated cap rate, as a fraction.</t>
+          <t>The stated sale price.</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -9561,35 +9561,119 @@
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
+          <t>om_sale_comp_price_per_unit</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D237" s="7" t="inlineStr">
+        <is>
+          <t>The stated price per unit.</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H237" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>om_sale_comp_cap_rate</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>The stated cap rate, as a fraction.</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H238" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
           <t>om_sale_comp_date</t>
         </is>
       </c>
-      <c r="C237" s="6" t="inlineStr">
+      <c r="C239" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D237" s="7" t="inlineStr">
+      <c r="D239" s="7" t="inlineStr">
         <is>
           <t>The sale date as written.</t>
         </is>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E239" s="6" t="inlineStr">
         <is>
           <t>Offering memorandum / marketing package</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
+      <c r="F239" s="7" t="inlineStr">
         <is>
           <t>Sale comps (institutional)</t>
         </is>
       </c>
-      <c r="G237" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H237" s="7" t="inlineStr">
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H239" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>1981</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>1,984</t>
+          <t>1984</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one.</t>
+          <t>Unit count where the registry has one. The registry was seeded from licensed data exports, so the public demo withholds it.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — Unit counts come from a licensed data export; the internal pipeline carries them.</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -9898,22 +9898,22 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>comps.rows</t>
+          <t>comps.nearby[].units</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>19 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape, via the market-report service</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -9924,94 +9924,94 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Own weekly scrape; asking and net effective stated separately.</t>
+          <t>Unit counts come from a licensed data export; the internal pipeline carries them.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>comps.rows.tier</t>
+          <t>comps.rows</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19 entries</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Tracked-community registry, via the market-report service</t>
+          <t>Operator's own weekly rent scrape, via the market-report service</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>comp_tiers.assign</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>comps.rows.distance_mi, comps.tiering.subject_product, comps.tiering.subject_year_built, comps.tiering.year_band, comps.tiering.top_n, comps.tiering.additional_n</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Closest same-product communities first, within the vintage band where the registry carries a year built; an unknown year keeps the community and says so.</t>
+          <t>Own weekly scrape; asking and net effective stated separately.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>demand.rings</t>
+          <t>comps.rows.tier</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>5 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
+          <t>Tracked-community registry, via the market-report service</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>comp_tiers.assign</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>comps.rows.distance_mi, comps.tiering.subject_product, comps.tiering.subject_year_built, comps.tiering.year_band, comps.tiering.top_n, comps.tiering.additional_n</t>
+        </is>
+      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Ring demographics.</t>
+          <t>Closest same-product communities first, within the vintage band where the registry carries a year built; an unknown year keeps the community and says so.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>demand.zip_home</t>
+          <t>demand.rings</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 entries</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
+          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -10027,29 +10027,29 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
+          <t>Ring demographics.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>om_comps.rent</t>
+          <t>demand.zip_home</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -10060,29 +10060,29 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
+          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>om_comps.rent</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -10093,24 +10093,24 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
+          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -10120,29 +10120,25 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
+          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.as_of</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -10152,40 +10148,44 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>as-of line</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Read as the end of the period the roll's own header states.</t>
+          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.lookback_months</t>
+          <t>rent_roll.as_of</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>as-of line</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -10196,19 +10196,19 @@
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
+          <t>Read as the end of the period the roll's own header states.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.new_tenant_tolerance_days</t>
+          <t>rent_roll.lookback_months</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -10229,29 +10229,29 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
+          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>rent_roll.new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>334 entries</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -10262,29 +10262,29 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Read from the uploaded rent roll.</t>
+          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>summary.address_provenance</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
+          <t>334 entries</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -10295,24 +10295,24 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Read from the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -10328,29 +10328,29 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -10361,29 +10361,29 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -10394,24 +10394,24 @@
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -10427,24 +10427,24 @@
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -10460,24 +10460,24 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -10493,24 +10493,24 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -10526,14 +10526,14 @@
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -10592,24 +10592,24 @@
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>1,456.99</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -10619,34 +10619,30 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Desert Ridge Capital Advisors</t>
+          <t>1,456.99</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -10656,30 +10652,34 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>1,344.6</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -10689,34 +10689,30 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n"/>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Phoenix MSA</t>
+          <t>1,344.6</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -10726,30 +10722,34 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -10765,29 +10765,29 @@
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -10797,6 +10797,39 @@
       </c>
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>summary.product_detail</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Sample Property Offering Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>the property offers a diversified mix of 
 one-, two-, and three-bedroom residences averaging 856 square 
@@ -10804,58 +10837,25 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>summary.product_type</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Garden-style multifamily</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>p.3</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Porter Elementary School</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Internal underwriting agent — attendance-zone school lookup</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -10866,19 +10866,19 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Mesa High School</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -10906,12 +10906,12 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Taylor Junior High School</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -10939,22 +10939,22 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Sonoran Residential Holdings LLC</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -10965,24 +10965,24 @@
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -10998,19 +10998,19 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -11038,22 +11038,22 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>1 &amp; 2 stories</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -11064,29 +11064,29 @@
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Number of Stories 1 &amp; 2</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -11097,29 +11097,29 @@
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Number of Stories 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Limited property value (LPV), per the county assessor</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -11130,19 +11130,19 @@
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>What the assessed basis is in this state.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -11163,29 +11163,29 @@
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>How the basis behaves on a sale, with the authority.</t>
+          <t>What the assessed basis is in this state.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>249,122</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -11196,19 +11196,19 @@
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>2025 Property Tax $249,122</t>
+          <t>How the basis behaves on a sale, with the authority.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>249,122</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -11236,22 +11236,22 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -11262,29 +11262,29 @@
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -11295,29 +11295,29 @@
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>301-04-002K</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -11328,56 +11328,52 @@
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>Tax Parcel Number 301-04-002K</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_per_unit_flag</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
+          <t>301-04-002K</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.band_check</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n"/>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+          <t>Tax Parcel Number 301-04-002K</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -11387,30 +11383,34 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_evidence</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -11420,34 +11420,30 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.evidence_text</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n"/>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_year</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -11457,147 +11453,151 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_statement_amount</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>239,566.79</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Property Taxes lines</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>t12.rows</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n"/>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>239,566.79</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>t12.rows</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>Counted from the rows of the uploaded rent roll.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Y ear Built 1981</t>
+          <t>Counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>1,981</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -11608,99 +11608,99 @@
       <c r="F62" s="12" t="n"/>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Y ear Built 1981</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>supply.projects</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>32 entries</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>supply.rings</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
+          <t>supply.projects</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>32 entries</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
           <t>supply.rings</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>8 entries</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>POST /report (format json)</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="n"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
+          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>supply.rings</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>8 entries</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -11711,19 +11711,19 @@
       <c r="F65" s="12" t="n"/>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Read from the uploaded statement.</t>
+          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>t12.month_labels</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>4 keys</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>header block</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -11742,17 +11742,21 @@
         </is>
       </c>
       <c r="F66" s="12" t="n"/>
-      <c r="G66" s="13" t="n"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>t12.source_subtotals</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>4 keys</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -11762,7 +11766,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>header block</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -11771,31 +11775,27 @@
         </is>
       </c>
       <c r="F67" s="12" t="n"/>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>Read from the uploaded statement.</t>
-        </is>
-      </c>
+      <c r="G67" s="13" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>trade_out.rows</t>
+          <t>t12.units</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -11805,6 +11805,39 @@
       </c>
       <c r="F68" s="12" t="n"/>
       <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>0 entries</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Internal pipeline only</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
+          <t>Comp vintage where one is published: the public property record's year where it has one, else the community registry's. Blank means nobody published one, never that the community is new.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>Where that year came from: the public record with its as-of, or the community registry (third-party market data). Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>vendor note on the tracked community record, via the market-report service</t>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Trails at Harris</t>
+          <t>The Village at Lindsay Park Apartments</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
+          <t>1441 S Lindsay Rd, Mesa, AZ 85204-6285</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one. The registry was seeded from licensed data exports, so the public demo withholds it.</t>
+          <t>Unit count. The registry's own count was seeded from licensed data exports, so the public demo withholds it and shows the public-record count instead where one exists (county property record, Florida DBPR apartment licence, City of Austin permit), with its source and as-of.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>Internal pipeline only — Unit counts come from a licensed data export; the internal pipeline carries them.</t>
+          <t>Public record where one exists — A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>256 — Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
+          <t>vintage 1997 is 16 years from the subject's 1981, outside the +/-10-year band</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>20,297</t>
+          <t>20,298</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>$79,735</t>
+          <t>$79,731</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>5,239</t>
+          <t>5,237</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>340 entries</t>
+          <t>343 entries</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -9924,7 +9924,7 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Unit counts come from a licensed data export; the internal pipeline carries them.</t>
+          <t>A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>19 entries</t>
+          <t>26 entries</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -10001,22 +10001,22 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>demand.rings</t>
+          <t>comps.rows[].units</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>5 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -10027,24 +10027,24 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Ring demographics.</t>
+          <t>A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>demand.zip_home</t>
+          <t>demand.rings</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 entries</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
+          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -10060,29 +10060,29 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
+          <t>Ring demographics.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>om_comps.rent</t>
+          <t>demand.zip_home</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -10093,29 +10093,29 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
+          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>om_comps.rent</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -10126,24 +10126,24 @@
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
+          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -10153,29 +10153,25 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
+          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.as_of</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -10185,40 +10181,44 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>as-of line</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Read as the end of the period the roll's own header states.</t>
+          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.lookback_months</t>
+          <t>rent_roll.as_of</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>as-of line</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -10229,19 +10229,19 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
+          <t>Read as the end of the period the roll's own header states.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.new_tenant_tolerance_days</t>
+          <t>rent_roll.lookback_months</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -10262,29 +10262,29 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
+          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>rent_roll.new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>334 entries</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -10295,29 +10295,29 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Read from the uploaded rent roll.</t>
+          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>summary.address_provenance</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
+          <t>334 entries</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -10328,24 +10328,24 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Read from the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -10361,29 +10361,29 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -10394,29 +10394,29 @@
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -10427,24 +10427,24 @@
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -10460,24 +10460,24 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -10493,24 +10493,24 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -10526,24 +10526,24 @@
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -10559,14 +10559,14 @@
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -10599,7 +10599,7 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -10625,24 +10625,24 @@
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>1,456.99</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -10652,34 +10652,30 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n"/>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Desert Ridge Capital Advisors</t>
+          <t>1,456.99</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -10689,30 +10685,34 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>1,344.6</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -10722,34 +10722,30 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n"/>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Phoenix MSA</t>
+          <t>1,344.6</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -10759,30 +10755,34 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -10798,29 +10798,29 @@
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -10830,6 +10830,39 @@
       </c>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>summary.product_detail</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Sample Property Offering Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>the property offers a diversified mix of 
 one-, two-, and three-bedroom residences averaging 856 square 
@@ -10837,58 +10870,25 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>summary.product_type</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Garden-style multifamily</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>p.3</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
-        </is>
-      </c>
-    </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Porter Elementary School</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Internal underwriting agent — attendance-zone school lookup</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -10899,19 +10899,19 @@
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Mesa High School</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -10939,12 +10939,12 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Taylor Junior High School</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -10972,22 +10972,22 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Sonoran Residential Holdings LLC</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -10998,24 +10998,24 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -11031,19 +11031,19 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -11064,29 +11064,29 @@
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>1 &amp; 2 stories</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -11097,29 +11097,29 @@
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Number of Stories 1 &amp; 2</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -11130,29 +11130,29 @@
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Number of Stories 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Limited property value (LPV), per the county assessor</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -11163,19 +11163,19 @@
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>What the assessed basis is in this state.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -11196,29 +11196,29 @@
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>How the basis behaves on a sale, with the authority.</t>
+          <t>What the assessed basis is in this state.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>249,122</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -11229,19 +11229,19 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>2025 Property Tax $249,122</t>
+          <t>How the basis behaves on a sale, with the authority.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>249,122</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -11269,22 +11269,22 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -11295,29 +11295,29 @@
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -11328,29 +11328,29 @@
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>301-04-002K</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -11361,56 +11361,52 @@
       <c r="F55" s="12" t="n"/>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>Tax Parcel Number 301-04-002K</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_per_unit_flag</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
+          <t>301-04-002K</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.band_check</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n"/>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+          <t>Tax Parcel Number 301-04-002K</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -11420,30 +11416,34 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_evidence</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -11453,34 +11453,30 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.evidence_text</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="n"/>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_rate_year</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -11490,147 +11486,151 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
+        </is>
+      </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>summary.tax_statement_amount</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>239,566.79</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Property Taxes lines</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>t12.rows</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n"/>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>239,566.79</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>t12.rows</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>Counted from the rows of the uploaded rent roll.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F62" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>Y ear Built 1981</t>
+          <t>Counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>1,981</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -11641,99 +11641,99 @@
       <c r="F63" s="12" t="n"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Y ear Built 1981</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>supply.projects</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>32 entries</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>supply.rings</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="n"/>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
+          <t>supply.projects</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>33 entries</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
           <t>supply.rings</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>8 entries</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>POST /report (format json)</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="n"/>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
+          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>supply.rings</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>8 entries</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -11744,19 +11744,19 @@
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>Read from the uploaded statement.</t>
+          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>t12.month_labels</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>4 keys</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>header block</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -11775,17 +11775,21 @@
         </is>
       </c>
       <c r="F67" s="12" t="n"/>
-      <c r="G67" s="13" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>t12.source_subtotals</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>4 keys</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -11795,7 +11799,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>header block</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -11804,31 +11808,27 @@
         </is>
       </c>
       <c r="F68" s="12" t="n"/>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Read from the uploaded statement.</t>
-        </is>
-      </c>
+      <c r="G68" s="13" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>trade_out.rows</t>
+          <t>t12.units</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -11838,6 +11838,39 @@
       </c>
       <c r="F69" s="12" t="n"/>
       <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>0 entries</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Internal pipeline only</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="n"/>
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
+++ b/public/downloads/underwriting-demo/sample-model-ready-outputs.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>Unit-weighted in-place rent across the property.</t>
+          <t>Mean contract rent over the occupied units with a stated contract rent (vacant units carry no in-place rent; an occupied unit with no stated rent is left out, not counted as zero).</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -7069,32 +7069,32 @@
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>cohort_prior_rent_effective</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Average prior rent after the prior lease's concession. Optional: absent when the report states no prior concession, and the prior gross stands in.</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Prior effective rent</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H175" s="7" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>cohort_gross_change_pct</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Gross change over prior rent.</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
@@ -7153,95 +7153,95 @@
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
+          <t>cohort_effective_change_pct</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Effective change over prior effective rent (the prior gross when no prior concession is stated).</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Rent growth evidence</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
           <t>absent_reason</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D177" s="7" t="inlineStr">
+      <c r="D178" s="7" t="inlineStr">
         <is>
           <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E178" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G177" s="7" t="inlineStr">
+      <c r="G178" s="7" t="inlineStr">
         <is>
           <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
-      <c r="H177" s="7" t="inlineStr">
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B178" s="5" t="n"/>
-      <c r="C178" s="5" t="n"/>
-      <c r="D178" s="5" t="n"/>
-      <c r="E178" s="5" t="n"/>
-      <c r="F178" s="5" t="n"/>
-      <c r="G178" s="5" t="n"/>
-      <c r="H178" s="5" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
-        <is>
-          <t>comp_community</t>
-        </is>
-      </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Comparable community name.</t>
-        </is>
-      </c>
-      <c r="E179" s="6" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H179" s="7" t="inlineStr">
-        <is>
-          <t>Saltera Apartments</t>
-        </is>
-      </c>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
+      <c r="H179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
@@ -7251,22 +7251,22 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>comp_distance_mi</t>
+          <t>comp_community</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>Straight-line distance from the subject.</t>
+          <t>Comparable community name.</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>Saltera Apartments</t>
         </is>
       </c>
     </row>
@@ -7293,22 +7293,22 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>comp_floor_plan</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>1BR — lowest five of 5 available</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -7335,22 +7335,22 @@
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>comp_tier</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D182" s="7" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published: the public property record's year where it has one, else the community registry's. Blank means nobody published one, never that the community is new.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7419,17 +7419,17 @@
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>comp_year_built_source</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D184" s="7" t="inlineStr">
         <is>
-          <t>Where that year came from: the public record with its as-of, or the community registry (third-party market data). Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>Comp vintage where one is published: the public property record's year where it has one, else the community registry's. Blank means nobody published one, never that the community is new.</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+          <t>1984</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>nearby_community</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
+          <t>Where that year came from: the public record with its as-of, or the community registry (third-party market data). Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>The Village at Lindsay Park Apartments</t>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>nearby_address</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Its address, so the reader can place it.</t>
+          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>1441 S Lindsay Rd, Mesa, AZ 85204-6285</t>
+          <t>The Village at Lindsay Park Apartments</t>
         </is>
       </c>
     </row>
@@ -7545,22 +7545,22 @@
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>nearby_distance_mi</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1441 S Lindsay Rd, Mesa, AZ 85204-6285</t>
         </is>
       </c>
     </row>
@@ -7587,22 +7587,22 @@
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>nearby_units</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Unit count. The registry's own count was seeded from licensed data exports, so the public demo withholds it and shows the public-record count instead where one exists (county property record, Florida DBPR apartment licence, City of Austin permit), with its source and as-of.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>Public record where one exists — A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>256 — Maricopa County, AZ property record, as of 2026-10-05</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -7629,22 +7629,22 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>nearby_reason</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
+          <t>Unit count. The registry's own count was seeded from licensed data exports, so the public demo withholds it and shows the public-record count instead where one exists (county property record, Florida DBPR apartment licence, City of Austin permit), with its source and as-of.</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Public record where one exists — A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>vintage 1997 is 16 years from the subject's 1981, outside the +/-10-year band</t>
+          <t>256 — Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>compset_vintage_footnote</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>Vintage filter: +/-10 years of the subject's year built.</t>
+          <t>vintage 1997 is 16 years from the subject's 1981, outside the +/-10-year band</t>
         </is>
       </c>
     </row>
@@ -7713,27 +7713,27 @@
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Vintage filter: +/-10 years of the subject's year built.</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="D192" s="7" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7839,17 +7839,17 @@
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D194" s="7" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>$1,200</t>
+          <t>688.0</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -7933,17 +7933,17 @@
       </c>
       <c r="D196" s="7" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>$1,200</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -8007,27 +8007,27 @@
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D198" s="7" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
@@ -8049,17 +8049,17 @@
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8091,17 +8091,17 @@
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D200" s="7" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -8133,27 +8133,27 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="D202" s="7" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -8217,95 +8217,95 @@
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
           <t>subject_vs_compset_spread</t>
         </is>
       </c>
-      <c r="C203" s="6" t="inlineStr">
+      <c r="C204" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D203" s="7" t="inlineStr">
+      <c r="D204" s="7" t="inlineStr">
         <is>
           <t>Subject market rent over comp-set net effective, less one.</t>
         </is>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E204" s="6" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F203" s="7" t="inlineStr">
+      <c r="F204" s="7" t="inlineStr">
         <is>
           <t>Rent positioning</t>
         </is>
       </c>
-      <c r="G203" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H203" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B204" s="5" t="n"/>
-      <c r="C204" s="5" t="n"/>
-      <c r="D204" s="5" t="n"/>
-      <c r="E204" s="5" t="n"/>
-      <c r="F204" s="5" t="n"/>
-      <c r="G204" s="5" t="n"/>
-      <c r="H204" s="5" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="6" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>demand_ring</t>
-        </is>
-      </c>
-      <c r="C205" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D205" s="7" t="inlineStr">
-        <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
-        </is>
-      </c>
-      <c r="E205" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F205" s="7" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G205" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H205" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
+      <c r="F205" s="5" t="n"/>
+      <c r="G205" s="5" t="n"/>
+      <c r="H205" s="5" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>demand_population</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D206" s="7" t="inlineStr">
         <is>
-          <t>Population in the ring.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>20,298</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>7,711</t>
+          <t>20,298</t>
         </is>
       </c>
     </row>
@@ -8399,17 +8399,17 @@
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D208" s="7" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>$79,731</t>
+          <t>7,711</t>
         </is>
       </c>
     </row>
@@ -8441,17 +8441,17 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G209" s="7" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>5,237</t>
+          <t>$79,731</t>
         </is>
       </c>
     </row>
@@ -8483,17 +8483,17 @@
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>demand_jobs</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D210" s="7" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Jobs located in the ring.</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G210" s="7" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>5,237</t>
         </is>
       </c>
     </row>
@@ -8525,95 +8525,95 @@
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
           <t>demand_renter_share</t>
         </is>
       </c>
-      <c r="C211" s="6" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D211" s="7" t="inlineStr">
+      <c r="D212" s="7" t="inlineStr">
         <is>
           <t>Share of ring households that rent.</t>
         </is>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="E212" s="6" t="inlineStr">
         <is>
           <t>Public demographic data</t>
         </is>
       </c>
-      <c r="F211" s="7" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>Demand context</t>
         </is>
       </c>
-      <c r="G211" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H211" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H212" s="7" t="inlineStr">
         <is>
           <t>43.4%</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="5" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B212" s="5" t="n"/>
-      <c r="C212" s="5" t="n"/>
-      <c r="D212" s="5" t="n"/>
-      <c r="E212" s="5" t="n"/>
-      <c r="F212" s="5" t="n"/>
-      <c r="G212" s="5" t="n"/>
-      <c r="H212" s="5" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
-        <is>
-          <t>supply_ring</t>
-        </is>
-      </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D213" s="7" t="inlineStr">
-        <is>
-          <t>Ring the supply row describes.</t>
-        </is>
-      </c>
-      <c r="E213" s="6" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F213" s="7" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G213" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H213" s="7" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="5" t="n"/>
+      <c r="F213" s="5" t="n"/>
+      <c r="G213" s="5" t="n"/>
+      <c r="H213" s="5" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>supply_stage</t>
+          <t>supply_ring</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="D214" s="7" t="inlineStr">
         <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
+          <t>Ring the supply row describes.</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -8665,17 +8665,17 @@
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>supply_stage</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>supply_projects</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="D216" s="7" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Projects at that ring and stage.</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>supply_units</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
@@ -8759,17 +8759,17 @@
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Units at that ring and stage.</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -8791,17 +8791,17 @@
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>supply_pct_of_ring_stock</t>
+          <t>supply_ring_total_units</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D218" s="7" t="inlineStr">
         <is>
-          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
+          <t>All pipeline units in the ring across stages.</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>Supply pressure</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
@@ -8833,27 +8833,27 @@
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>supply_project_name</t>
+          <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
+          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Supply pressure</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>Reed Park Residences</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8875,22 +8875,22 @@
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>supply_project_miles</t>
+          <t>supply_project_name</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D220" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
+          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>Reed Park Residences</t>
         </is>
       </c>
     </row>
@@ -8917,22 +8917,22 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>supply_project_stage</t>
+          <t>supply_project_miles</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
+          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -8959,17 +8959,17 @@
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>supply_project_units</t>
+          <t>supply_project_stage</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D222" s="7" t="inlineStr">
         <is>
-          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
+          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -9001,17 +9001,17 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>supply_project_product</t>
+          <t>supply_project_units</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Product the pipeline records for the development.</t>
+          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>supply_project_address</t>
+          <t>supply_project_product</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="D224" s="7" t="inlineStr">
         <is>
-          <t>Street address where a layer carried one.</t>
+          <t>Product the pipeline records for the development.</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>multifamily</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>supply_project_city</t>
+          <t>supply_project_address</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="D225" s="7" t="inlineStr">
         <is>
-          <t>City where a layer carried one.</t>
+          <t>Street address where a layer carried one.</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
@@ -9127,17 +9127,17 @@
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>supply_project_acres</t>
+          <t>supply_project_city</t>
         </is>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D226" s="7" t="inlineStr">
         <is>
-          <t>Site acreage where a layer carried one.</t>
+          <t>City where a layer carried one.</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="H226" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9169,17 +9169,17 @@
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>supply_project_developer</t>
+          <t>supply_project_acres</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D227" s="7" t="inlineStr">
         <is>
-          <t>Developer where a layer named one.</t>
+          <t>Site acreage where a layer carried one.</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
@@ -9211,17 +9211,17 @@
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>supply_project_filed</t>
+          <t>supply_project_developer</t>
         </is>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D228" s="7" t="inlineStr">
         <is>
-          <t>Earliest filing date across the layers the development appears on.</t>
+          <t>Developer where a layer named one.</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="H228" s="7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>supply_project_latest</t>
+          <t>supply_project_filed</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>Latest activity date across those layers.</t>
+          <t>Earliest filing date across the layers the development appears on.</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
@@ -9295,95 +9295,95 @@
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
+          <t>supply_project_latest</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>Latest activity date across those layers.</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
           <t>supply_project_layers</t>
         </is>
       </c>
-      <c r="C230" s="6" t="inlineStr">
+      <c r="C231" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D230" s="7" t="inlineStr">
+      <c r="D231" s="7" t="inlineStr">
         <is>
           <t>The pipeline layers the development appeared on. Layers are lifecycle views of the same market, so one development can appear on several and is counted once.</t>
         </is>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E231" s="6" t="inlineStr">
         <is>
           <t>Public permit / entitlement records</t>
         </is>
       </c>
-      <c r="F230" s="7" t="inlineStr">
+      <c r="F231" s="7" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G230" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H230" s="7" t="inlineStr">
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
         <is>
           <t>1 entries</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="5" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
         <is>
           <t>OM comparables</t>
         </is>
       </c>
-      <c r="B231" s="5" t="n"/>
-      <c r="C231" s="5" t="n"/>
-      <c r="D231" s="5" t="n"/>
-      <c r="E231" s="5" t="n"/>
-      <c r="F231" s="5" t="n"/>
-      <c r="G231" s="5" t="n"/>
-      <c r="H231" s="5" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="6" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B232" s="6" t="inlineStr">
-        <is>
-          <t>om_rent_comp_community</t>
-        </is>
-      </c>
-      <c r="C232" s="6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D232" s="7" t="inlineStr">
-        <is>
-          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
-        </is>
-      </c>
-      <c r="E232" s="6" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F232" s="7" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G232" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H232" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="5" t="n"/>
+      <c r="F232" s="5" t="n"/>
+      <c r="G232" s="5" t="n"/>
+      <c r="H232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -9393,17 +9393,17 @@
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>om_rent_comp_distance_mi</t>
+          <t>om_rent_comp_community</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D233" s="7" t="inlineStr">
         <is>
-          <t>Distance from the subject as the memorandum states it.</t>
+          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
@@ -9435,17 +9435,17 @@
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>om_rent_comp_rent</t>
+          <t>om_rent_comp_distance_mi</t>
         </is>
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D234" s="7" t="inlineStr">
         <is>
-          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
+          <t>Distance from the subject as the memorandum states it.</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -9477,17 +9477,17 @@
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_property</t>
+          <t>om_rent_comp_rent</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D235" s="7" t="inlineStr">
         <is>
-          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G235" s="7" t="inlineStr">
@@ -9519,17 +9519,17 @@
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price</t>
+          <t>om_sale_comp_property</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D236" s="7" t="inlineStr">
         <is>
-          <t>The stated sale price.</t>
+          <t>A whole-community sale comparable the memorandum cites, by name.</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_price_per_unit</t>
+          <t>om_sale_comp_price</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D237" s="7" t="inlineStr">
         <is>
-          <t>The stated price per unit.</t>
+          <t>The stated sale price.</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
@@ -9603,17 +9603,17 @@
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>om_sale_comp_cap_rate</t>
+          <t>om_sale_comp_price_per_unit</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>The stated cap rate, as a fraction.</t>
+          <t>The stated price per unit.</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -9645,35 +9645,77 @@
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
+          <t>om_sale_comp_cap_rate</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>The stated cap rate, as a fraction.</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H239" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
           <t>om_sale_comp_date</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
+      <c r="C240" s="6" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D239" s="7" t="inlineStr">
+      <c r="D240" s="7" t="inlineStr">
         <is>
           <t>The sale date as written.</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>Offering memorandum / marketing package</t>
         </is>
       </c>
-      <c r="F239" s="7" t="inlineStr">
+      <c r="F240" s="7" t="inlineStr">
         <is>
           <t>Sale comps (institutional)</t>
         </is>
       </c>
-      <c r="G239" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H239" s="7" t="inlineStr">
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H240" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
